--- a/artfynd/A 6315-2025 artfynd.xlsx
+++ b/artfynd/A 6315-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY36"/>
+  <dimension ref="A1:AY42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4886,6 +4886,673 @@
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>123025220</v>
+      </c>
+      <c r="B37" t="n">
+        <v>95903</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>53</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Svarttjärnen 3, Vimyrens naturreservat, Vrm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>404769</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6686816</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>En låga med riklig förekomst på</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Sofia Damne</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Sofia Damne</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>123025268</v>
+      </c>
+      <c r="B38" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Svarttjärnen 4, Vimyrens naturreservat, Vrm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>404828</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6686867</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Sofia Damne</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Sofia Damne</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>123025288</v>
+      </c>
+      <c r="B39" t="n">
+        <v>78503</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Svarttjärnen 5, Vimyrens naturreservat, Vrm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>404846</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6686878</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Sofia Damne</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Sofia Damne</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>123024336</v>
+      </c>
+      <c r="B40" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Svarttjärnen 1, Vimyrens naturreservat, Vrm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>404722</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6686761</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Sofia Damne</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Sofia Damne</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>123024872</v>
+      </c>
+      <c r="B41" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Svarttjärnen 2, Vimyrens naturreservat, Vrm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>404740</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6686776</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Sofia Damne</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Sofia Damne</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>123025199</v>
+      </c>
+      <c r="B42" t="n">
+        <v>95021</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>2170</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Flagellkvastmossa</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Dicranum flagellare</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Svarttjärnen 3, Vimyrens naturreservat, Vrm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>404769</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6686816</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Sofia Damne</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Sofia Damne</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 6315-2025 artfynd.xlsx
+++ b/artfynd/A 6315-2025 artfynd.xlsx
@@ -4888,10 +4888,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123025220</v>
+        <v>123025199</v>
       </c>
       <c r="B37" t="n">
-        <v>95903</v>
+        <v>95021</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4900,25 +4900,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>53</v>
+        <v>2170</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -4974,11 +4974,6 @@
           <t>2025-03-07</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>En låga med riklig förekomst på</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -5004,10 +4999,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123025268</v>
+        <v>123025288</v>
       </c>
       <c r="B38" t="n">
-        <v>78766</v>
+        <v>78503</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5020,26 +5015,26 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J38" t="inlineStr"/>
@@ -5047,14 +5042,14 @@
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Svarttjärnen 4, Vimyrens naturreservat, Vrm</t>
+          <t>Svarttjärnen 5, Vimyrens naturreservat, Vrm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>404828</v>
+        <v>404846</v>
       </c>
       <c r="R38" t="n">
-        <v>6686867</v>
+        <v>6686878</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5114,10 +5109,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123025288</v>
+        <v>123025220</v>
       </c>
       <c r="B39" t="n">
-        <v>78503</v>
+        <v>95903</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5130,21 +5125,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228912</v>
+        <v>53</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -5154,17 +5149,18 @@
       </c>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Svarttjärnen 5, Vimyrens naturreservat, Vrm</t>
+          <t>Svarttjärnen 3, Vimyrens naturreservat, Vrm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>404846</v>
+        <v>404769</v>
       </c>
       <c r="R39" t="n">
-        <v>6686878</v>
+        <v>6686816</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5197,6 +5193,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>En låga med riklig förekomst på</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5224,7 +5225,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123024336</v>
+        <v>123024872</v>
       </c>
       <c r="B40" t="n">
         <v>78766</v>
@@ -5267,14 +5268,14 @@
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Svarttjärnen 1, Vimyrens naturreservat, Vrm</t>
+          <t>Svarttjärnen 2, Vimyrens naturreservat, Vrm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>404722</v>
+        <v>404740</v>
       </c>
       <c r="R40" t="n">
-        <v>6686761</v>
+        <v>6686776</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5334,7 +5335,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123024872</v>
+        <v>123025268</v>
       </c>
       <c r="B41" t="n">
         <v>78766</v>
@@ -5369,7 +5370,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J41" t="inlineStr"/>
@@ -5377,14 +5378,14 @@
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Svarttjärnen 2, Vimyrens naturreservat, Vrm</t>
+          <t>Svarttjärnen 4, Vimyrens naturreservat, Vrm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>404740</v>
+        <v>404828</v>
       </c>
       <c r="R41" t="n">
-        <v>6686776</v>
+        <v>6686867</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5444,10 +5445,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123025199</v>
+        <v>123024336</v>
       </c>
       <c r="B42" t="n">
-        <v>95021</v>
+        <v>78766</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5456,25 +5457,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2170</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -5484,18 +5485,17 @@
       </c>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Svarttjärnen 3, Vimyrens naturreservat, Vrm</t>
+          <t>Svarttjärnen 1, Vimyrens naturreservat, Vrm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>404769</v>
+        <v>404722</v>
       </c>
       <c r="R42" t="n">
-        <v>6686816</v>
+        <v>6686761</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>

--- a/artfynd/A 6315-2025 artfynd.xlsx
+++ b/artfynd/A 6315-2025 artfynd.xlsx
@@ -4888,10 +4888,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123025199</v>
+        <v>123025288</v>
       </c>
       <c r="B37" t="n">
-        <v>95021</v>
+        <v>78503</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4900,25 +4900,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2170</v>
+        <v>228912</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -4928,18 +4928,17 @@
       </c>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Svarttjärnen 3, Vimyrens naturreservat, Vrm</t>
+          <t>Svarttjärnen 5, Vimyrens naturreservat, Vrm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>404769</v>
+        <v>404846</v>
       </c>
       <c r="R37" t="n">
-        <v>6686816</v>
+        <v>6686878</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4999,10 +4998,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123025288</v>
+        <v>123024872</v>
       </c>
       <c r="B38" t="n">
-        <v>78503</v>
+        <v>78766</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5015,21 +5014,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -5042,14 +5041,14 @@
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Svarttjärnen 5, Vimyrens naturreservat, Vrm</t>
+          <t>Svarttjärnen 2, Vimyrens naturreservat, Vrm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>404846</v>
+        <v>404740</v>
       </c>
       <c r="R38" t="n">
-        <v>6686878</v>
+        <v>6686776</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5109,10 +5108,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123025220</v>
+        <v>123025268</v>
       </c>
       <c r="B39" t="n">
-        <v>95903</v>
+        <v>78766</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5125,42 +5124,41 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Svarttjärnen 3, Vimyrens naturreservat, Vrm</t>
+          <t>Svarttjärnen 4, Vimyrens naturreservat, Vrm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>404769</v>
+        <v>404828</v>
       </c>
       <c r="R39" t="n">
-        <v>6686816</v>
+        <v>6686867</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5193,11 +5191,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-03-07</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>En låga med riklig förekomst på</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5225,7 +5218,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123024872</v>
+        <v>123024336</v>
       </c>
       <c r="B40" t="n">
         <v>78766</v>
@@ -5268,14 +5261,14 @@
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Svarttjärnen 2, Vimyrens naturreservat, Vrm</t>
+          <t>Svarttjärnen 1, Vimyrens naturreservat, Vrm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>404740</v>
+        <v>404722</v>
       </c>
       <c r="R40" t="n">
-        <v>6686776</v>
+        <v>6686761</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5335,57 +5328,58 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123025268</v>
+        <v>123025199</v>
       </c>
       <c r="B41" t="n">
-        <v>78766</v>
+        <v>95021</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>2170</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Svarttjärnen 4, Vimyrens naturreservat, Vrm</t>
+          <t>Svarttjärnen 3, Vimyrens naturreservat, Vrm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>404828</v>
+        <v>404769</v>
       </c>
       <c r="R41" t="n">
-        <v>6686867</v>
+        <v>6686816</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5445,14 +5439,14 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123024336</v>
+        <v>123025220</v>
       </c>
       <c r="B42" t="n">
-        <v>78766</v>
+        <v>95903</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5461,21 +5455,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -5485,17 +5479,18 @@
       </c>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Svarttjärnen 1, Vimyrens naturreservat, Vrm</t>
+          <t>Svarttjärnen 3, Vimyrens naturreservat, Vrm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>404722</v>
+        <v>404769</v>
       </c>
       <c r="R42" t="n">
-        <v>6686761</v>
+        <v>6686816</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5528,6 +5523,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>En låga med riklig förekomst på</t>
         </is>
       </c>
       <c r="AD42" t="b">

--- a/artfynd/A 6315-2025 artfynd.xlsx
+++ b/artfynd/A 6315-2025 artfynd.xlsx
@@ -4998,7 +4998,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123024872</v>
+        <v>123025268</v>
       </c>
       <c r="B38" t="n">
         <v>78766</v>
@@ -5033,7 +5033,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J38" t="inlineStr"/>
@@ -5041,14 +5041,14 @@
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Svarttjärnen 2, Vimyrens naturreservat, Vrm</t>
+          <t>Svarttjärnen 4, Vimyrens naturreservat, Vrm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>404740</v>
+        <v>404828</v>
       </c>
       <c r="R38" t="n">
-        <v>6686776</v>
+        <v>6686867</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5108,7 +5108,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123025268</v>
+        <v>123024872</v>
       </c>
       <c r="B39" t="n">
         <v>78766</v>
@@ -5143,7 +5143,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J39" t="inlineStr"/>
@@ -5151,14 +5151,14 @@
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Svarttjärnen 4, Vimyrens naturreservat, Vrm</t>
+          <t>Svarttjärnen 2, Vimyrens naturreservat, Vrm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>404828</v>
+        <v>404740</v>
       </c>
       <c r="R39" t="n">
-        <v>6686867</v>
+        <v>6686776</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5331,7 +5331,7 @@
         <v>123025199</v>
       </c>
       <c r="B41" t="n">
-        <v>95021</v>
+        <v>95029</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5442,7 +5442,7 @@
         <v>123025220</v>
       </c>
       <c r="B42" t="n">
-        <v>95903</v>
+        <v>95911</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>

--- a/artfynd/A 6315-2025 artfynd.xlsx
+++ b/artfynd/A 6315-2025 artfynd.xlsx
@@ -4888,10 +4888,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123025288</v>
+        <v>123025268</v>
       </c>
       <c r="B37" t="n">
-        <v>78503</v>
+        <v>78766</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4904,26 +4904,26 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J37" t="inlineStr"/>
@@ -4931,14 +4931,14 @@
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Svarttjärnen 5, Vimyrens naturreservat, Vrm</t>
+          <t>Svarttjärnen 4, Vimyrens naturreservat, Vrm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>404846</v>
+        <v>404828</v>
       </c>
       <c r="R37" t="n">
-        <v>6686878</v>
+        <v>6686867</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4998,7 +4998,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123025268</v>
+        <v>123024872</v>
       </c>
       <c r="B38" t="n">
         <v>78766</v>
@@ -5033,7 +5033,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J38" t="inlineStr"/>
@@ -5041,14 +5041,14 @@
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Svarttjärnen 4, Vimyrens naturreservat, Vrm</t>
+          <t>Svarttjärnen 2, Vimyrens naturreservat, Vrm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>404828</v>
+        <v>404740</v>
       </c>
       <c r="R38" t="n">
-        <v>6686867</v>
+        <v>6686776</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5108,7 +5108,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123024872</v>
+        <v>123024336</v>
       </c>
       <c r="B39" t="n">
         <v>78766</v>
@@ -5151,14 +5151,14 @@
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Svarttjärnen 2, Vimyrens naturreservat, Vrm</t>
+          <t>Svarttjärnen 1, Vimyrens naturreservat, Vrm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>404740</v>
+        <v>404722</v>
       </c>
       <c r="R39" t="n">
-        <v>6686776</v>
+        <v>6686761</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5218,10 +5218,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123024336</v>
+        <v>123025288</v>
       </c>
       <c r="B40" t="n">
-        <v>78766</v>
+        <v>78503</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5234,21 +5234,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -5261,14 +5261,14 @@
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Svarttjärnen 1, Vimyrens naturreservat, Vrm</t>
+          <t>Svarttjärnen 5, Vimyrens naturreservat, Vrm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>404722</v>
+        <v>404846</v>
       </c>
       <c r="R40" t="n">
-        <v>6686761</v>
+        <v>6686878</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5328,10 +5328,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123025199</v>
+        <v>123025220</v>
       </c>
       <c r="B41" t="n">
-        <v>95029</v>
+        <v>95911</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5340,25 +5340,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2170</v>
+        <v>53</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -5414,6 +5414,11 @@
           <t>2025-03-07</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>En låga med riklig förekomst på</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5439,10 +5444,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123025220</v>
+        <v>123025199</v>
       </c>
       <c r="B42" t="n">
-        <v>95911</v>
+        <v>95029</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5451,25 +5456,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>53</v>
+        <v>2170</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -5523,11 +5528,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-03-07</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>En låga med riklig förekomst på</t>
         </is>
       </c>
       <c r="AD42" t="b">

--- a/artfynd/A 6315-2025 artfynd.xlsx
+++ b/artfynd/A 6315-2025 artfynd.xlsx
@@ -4888,7 +4888,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123025268</v>
+        <v>123024336</v>
       </c>
       <c r="B37" t="n">
         <v>78766</v>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J37" t="inlineStr"/>
@@ -4931,14 +4931,14 @@
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Svarttjärnen 4, Vimyrens naturreservat, Vrm</t>
+          <t>Svarttjärnen 1, Vimyrens naturreservat, Vrm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>404828</v>
+        <v>404722</v>
       </c>
       <c r="R37" t="n">
-        <v>6686867</v>
+        <v>6686761</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5108,10 +5108,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123024336</v>
+        <v>123025288</v>
       </c>
       <c r="B39" t="n">
-        <v>78766</v>
+        <v>78503</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5124,21 +5124,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -5151,14 +5151,14 @@
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Svarttjärnen 1, Vimyrens naturreservat, Vrm</t>
+          <t>Svarttjärnen 5, Vimyrens naturreservat, Vrm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>404722</v>
+        <v>404846</v>
       </c>
       <c r="R39" t="n">
-        <v>6686761</v>
+        <v>6686878</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5218,10 +5218,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123025288</v>
+        <v>123025268</v>
       </c>
       <c r="B40" t="n">
-        <v>78503</v>
+        <v>78766</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5234,26 +5234,26 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J40" t="inlineStr"/>
@@ -5261,14 +5261,14 @@
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Svarttjärnen 5, Vimyrens naturreservat, Vrm</t>
+          <t>Svarttjärnen 4, Vimyrens naturreservat, Vrm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>404846</v>
+        <v>404828</v>
       </c>
       <c r="R40" t="n">
-        <v>6686878</v>
+        <v>6686867</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5328,10 +5328,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123025220</v>
+        <v>123025199</v>
       </c>
       <c r="B41" t="n">
-        <v>95911</v>
+        <v>95029</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5340,25 +5340,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>53</v>
+        <v>2170</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -5414,11 +5414,6 @@
           <t>2025-03-07</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>En låga med riklig förekomst på</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5444,10 +5439,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123025199</v>
+        <v>123025220</v>
       </c>
       <c r="B42" t="n">
-        <v>95029</v>
+        <v>95911</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5456,25 +5451,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2170</v>
+        <v>53</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -5528,6 +5523,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>En låga med riklig förekomst på</t>
         </is>
       </c>
       <c r="AD42" t="b">

--- a/artfynd/A 6315-2025 artfynd.xlsx
+++ b/artfynd/A 6315-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY42"/>
+  <dimension ref="A1:AY71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5328,10 +5328,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123025199</v>
+        <v>123025220</v>
       </c>
       <c r="B41" t="n">
-        <v>95029</v>
+        <v>95911</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5340,25 +5340,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2170</v>
+        <v>53</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -5414,6 +5414,11 @@
           <t>2025-03-07</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>En låga med riklig förekomst på</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5439,10 +5444,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123025220</v>
+        <v>123025199</v>
       </c>
       <c r="B42" t="n">
-        <v>95911</v>
+        <v>95029</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5451,25 +5456,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>53</v>
+        <v>2170</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -5525,11 +5530,6 @@
           <t>2025-03-07</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>En låga med riklig förekomst på</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5552,6 +5552,2964 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>123302259</v>
+      </c>
+      <c r="B43" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Öster om Vimyrens naturreservat, Vrm</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>404680</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6686815</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>123302244</v>
+      </c>
+      <c r="B44" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Öster om Vimyrens naturreservat, Vrm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>404831</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6686961</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>123302237</v>
+      </c>
+      <c r="B45" t="n">
+        <v>78502</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Öster om Vimyrens naturreservat, Vrm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>404784</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6686893</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>123302258</v>
+      </c>
+      <c r="B46" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Öster om Vimyrens naturreservat, Vrm</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>404812</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6686926</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>123302255</v>
+      </c>
+      <c r="B47" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Öster om Vimyrens naturreservat, Vrm</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>404742</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6686791</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>123302241</v>
+      </c>
+      <c r="B48" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Öster om Vimyrens naturreservat, Vrm</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>404765</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6686893</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>123302250</v>
+      </c>
+      <c r="B49" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Öster om Vimyrens naturreservat, Vrm</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>404749</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6686779</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>123302239</v>
+      </c>
+      <c r="B50" t="n">
+        <v>95911</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>53</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Öster om Vimyrens naturreservat, Vrm</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>404942</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6686972</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>123302263</v>
+      </c>
+      <c r="B51" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Öster om Vimyrens naturreservat, Vrm</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>405174</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6687209</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>123302247</v>
+      </c>
+      <c r="B52" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Öster om Vimyrens naturreservat, Vrm</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>404900</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6686936</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>123302235</v>
+      </c>
+      <c r="B53" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Öster om Vimyrens naturreservat, Vrm</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>404825</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6686897</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>123302254</v>
+      </c>
+      <c r="B54" t="n">
+        <v>95911</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>53</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Öster om Vimyrens naturreservat, Vrm</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>404893</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6687000</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>123302242</v>
+      </c>
+      <c r="B55" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Öster om Vimyrens naturreservat, Vrm</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>404779</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6686907</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>123302236</v>
+      </c>
+      <c r="B56" t="n">
+        <v>78503</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Öster om Vimyrens naturreservat, Vrm</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>404784</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6686893</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>123302257</v>
+      </c>
+      <c r="B57" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Öster om Vimyrens naturreservat, Vrm</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>404825</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6686922</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>123302238</v>
+      </c>
+      <c r="B58" t="n">
+        <v>92233</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Öster om Vimyrens naturreservat, Vrm</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>404664</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6686821</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>123302256</v>
+      </c>
+      <c r="B59" t="n">
+        <v>92233</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Öster om Vimyrens naturreservat, Vrm</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>404740</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6686779</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>123302248</v>
+      </c>
+      <c r="B60" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Öster om Vimyrens naturreservat, Vrm</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>404485</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6686609</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>123302261</v>
+      </c>
+      <c r="B61" t="n">
+        <v>78503</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Öster om Vimyrens naturreservat, Vrm</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>404755</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6686809</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>123302252</v>
+      </c>
+      <c r="B62" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Öster om Vimyrens naturreservat, Vrm</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>404884</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6686940</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>123302240</v>
+      </c>
+      <c r="B63" t="n">
+        <v>95911</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>53</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Öster om Vimyrens naturreservat, Vrm</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>404906</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6686997</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>123302243</v>
+      </c>
+      <c r="B64" t="n">
+        <v>82553</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Öster om Vimyrens naturreservat, Vrm</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>404663</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6686805</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>123302264</v>
+      </c>
+      <c r="B65" t="n">
+        <v>92268</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Öster om Vimyrens naturreservat, Vrm</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>405076</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6687116</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>123302253</v>
+      </c>
+      <c r="B66" t="n">
+        <v>95911</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>53</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Öster om Vimyrens naturreservat, Vrm</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>404899</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6686991</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>123302262</v>
+      </c>
+      <c r="B67" t="n">
+        <v>78502</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Öster om Vimyrens naturreservat, Vrm</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>404991</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6687033</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>123302246</v>
+      </c>
+      <c r="B68" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Öster om Vimyrens naturreservat, Vrm</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>404908</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6687022</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>123302251</v>
+      </c>
+      <c r="B69" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Öster om Vimyrens naturreservat, Vrm</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>404754</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6686824</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>123302234</v>
+      </c>
+      <c r="B70" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Öster om Vimyrens naturreservat, Vrm</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>404896</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6686928</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>123302249</v>
+      </c>
+      <c r="B71" t="n">
+        <v>95911</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>53</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Öster om Vimyrens naturreservat, Vrm</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>404925</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6687022</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-03-18</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 6315-2025 artfynd.xlsx
+++ b/artfynd/A 6315-2025 artfynd.xlsx
@@ -4888,10 +4888,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123024336</v>
+        <v>123025268</v>
       </c>
       <c r="B37" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J37" t="inlineStr"/>
@@ -4931,14 +4931,14 @@
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Svarttjärnen 1, Vimyrens naturreservat, Vrm</t>
+          <t>Svarttjärnen 4, Vimyrens naturreservat, Vrm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>404722</v>
+        <v>404828</v>
       </c>
       <c r="R37" t="n">
-        <v>6686761</v>
+        <v>6686867</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4998,10 +4998,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123024872</v>
+        <v>123024336</v>
       </c>
       <c r="B38" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5041,14 +5041,14 @@
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Svarttjärnen 2, Vimyrens naturreservat, Vrm</t>
+          <t>Svarttjärnen 1, Vimyrens naturreservat, Vrm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>404740</v>
+        <v>404722</v>
       </c>
       <c r="R38" t="n">
-        <v>6686776</v>
+        <v>6686761</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5111,7 +5111,7 @@
         <v>123025288</v>
       </c>
       <c r="B39" t="n">
-        <v>78503</v>
+        <v>78506</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5218,10 +5218,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123025268</v>
+        <v>123024872</v>
       </c>
       <c r="B40" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5253,7 +5253,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J40" t="inlineStr"/>
@@ -5261,14 +5261,14 @@
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Svarttjärnen 4, Vimyrens naturreservat, Vrm</t>
+          <t>Svarttjärnen 2, Vimyrens naturreservat, Vrm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>404828</v>
+        <v>404740</v>
       </c>
       <c r="R40" t="n">
-        <v>6686867</v>
+        <v>6686776</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5331,7 +5331,7 @@
         <v>123025220</v>
       </c>
       <c r="B41" t="n">
-        <v>95911</v>
+        <v>95914</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5447,7 +5447,7 @@
         <v>123025199</v>
       </c>
       <c r="B42" t="n">
-        <v>95029</v>
+        <v>95032</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5555,10 +5555,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123302259</v>
+        <v>123302247</v>
       </c>
       <c r="B43" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>404680</v>
+        <v>404900</v>
       </c>
       <c r="R43" t="n">
-        <v>6686815</v>
+        <v>6686936</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5657,10 +5657,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123302244</v>
+        <v>123302240</v>
       </c>
       <c r="B44" t="n">
-        <v>78766</v>
+        <v>95914</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5673,21 +5673,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5697,10 +5697,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>404831</v>
+        <v>404906</v>
       </c>
       <c r="R44" t="n">
-        <v>6686961</v>
+        <v>6686997</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5759,10 +5759,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123302237</v>
+        <v>123302238</v>
       </c>
       <c r="B45" t="n">
-        <v>78502</v>
+        <v>92236</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5771,25 +5771,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5799,10 +5799,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>404784</v>
+        <v>404664</v>
       </c>
       <c r="R45" t="n">
-        <v>6686893</v>
+        <v>6686821</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5861,10 +5861,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123302258</v>
+        <v>123302251</v>
       </c>
       <c r="B46" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5901,10 +5901,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>404812</v>
+        <v>404754</v>
       </c>
       <c r="R46" t="n">
-        <v>6686926</v>
+        <v>6686824</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5963,10 +5963,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123302255</v>
+        <v>123302259</v>
       </c>
       <c r="B47" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6003,10 +6003,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>404742</v>
+        <v>404680</v>
       </c>
       <c r="R47" t="n">
-        <v>6686791</v>
+        <v>6686815</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6065,10 +6065,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123302241</v>
+        <v>123302250</v>
       </c>
       <c r="B48" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6105,10 +6105,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>404765</v>
+        <v>404749</v>
       </c>
       <c r="R48" t="n">
-        <v>6686893</v>
+        <v>6686779</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6167,10 +6167,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123302250</v>
+        <v>123302258</v>
       </c>
       <c r="B49" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6207,10 +6207,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>404749</v>
+        <v>404812</v>
       </c>
       <c r="R49" t="n">
-        <v>6686779</v>
+        <v>6686926</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6269,10 +6269,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123302239</v>
+        <v>123302244</v>
       </c>
       <c r="B50" t="n">
-        <v>95911</v>
+        <v>78769</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6285,21 +6285,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6309,10 +6309,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>404942</v>
+        <v>404831</v>
       </c>
       <c r="R50" t="n">
-        <v>6686972</v>
+        <v>6686961</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6371,10 +6371,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123302263</v>
+        <v>123302234</v>
       </c>
       <c r="B51" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6411,10 +6411,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>405174</v>
+        <v>404896</v>
       </c>
       <c r="R51" t="n">
-        <v>6687209</v>
+        <v>6686928</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6473,10 +6473,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123302247</v>
+        <v>123302239</v>
       </c>
       <c r="B52" t="n">
-        <v>78766</v>
+        <v>95914</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6489,21 +6489,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6513,10 +6513,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>404900</v>
+        <v>404942</v>
       </c>
       <c r="R52" t="n">
-        <v>6686936</v>
+        <v>6686972</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6575,10 +6575,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123302235</v>
+        <v>123302236</v>
       </c>
       <c r="B53" t="n">
-        <v>78766</v>
+        <v>78506</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6591,21 +6591,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6615,10 +6615,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>404825</v>
+        <v>404784</v>
       </c>
       <c r="R53" t="n">
-        <v>6686897</v>
+        <v>6686893</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6677,10 +6677,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123302254</v>
+        <v>123302242</v>
       </c>
       <c r="B54" t="n">
-        <v>95911</v>
+        <v>78769</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6693,21 +6693,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6717,10 +6717,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>404893</v>
+        <v>404779</v>
       </c>
       <c r="R54" t="n">
-        <v>6687000</v>
+        <v>6686907</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6779,10 +6779,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123302242</v>
+        <v>123302243</v>
       </c>
       <c r="B55" t="n">
-        <v>78766</v>
+        <v>82556</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6795,21 +6795,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6819,10 +6819,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>404779</v>
+        <v>404663</v>
       </c>
       <c r="R55" t="n">
-        <v>6686907</v>
+        <v>6686805</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6881,10 +6881,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123302236</v>
+        <v>123302261</v>
       </c>
       <c r="B56" t="n">
-        <v>78503</v>
+        <v>78506</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6921,10 +6921,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>404784</v>
+        <v>404755</v>
       </c>
       <c r="R56" t="n">
-        <v>6686893</v>
+        <v>6686809</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6983,10 +6983,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123302257</v>
+        <v>123302263</v>
       </c>
       <c r="B57" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7023,10 +7023,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>404825</v>
+        <v>405174</v>
       </c>
       <c r="R57" t="n">
-        <v>6686922</v>
+        <v>6687209</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7085,10 +7085,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123302238</v>
+        <v>123302255</v>
       </c>
       <c r="B58" t="n">
-        <v>92233</v>
+        <v>78769</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7097,25 +7097,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7125,10 +7125,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>404664</v>
+        <v>404742</v>
       </c>
       <c r="R58" t="n">
-        <v>6686821</v>
+        <v>6686791</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7187,10 +7187,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123302256</v>
+        <v>123302262</v>
       </c>
       <c r="B59" t="n">
-        <v>92233</v>
+        <v>78505</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7199,25 +7199,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7227,10 +7227,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>404740</v>
+        <v>404991</v>
       </c>
       <c r="R59" t="n">
-        <v>6686779</v>
+        <v>6687033</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7289,10 +7289,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123302248</v>
+        <v>123302252</v>
       </c>
       <c r="B60" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7329,10 +7329,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>404485</v>
+        <v>404884</v>
       </c>
       <c r="R60" t="n">
-        <v>6686609</v>
+        <v>6686940</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7391,10 +7391,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123302261</v>
+        <v>123302235</v>
       </c>
       <c r="B61" t="n">
-        <v>78503</v>
+        <v>78769</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7407,21 +7407,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7431,10 +7431,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>404755</v>
+        <v>404825</v>
       </c>
       <c r="R61" t="n">
-        <v>6686809</v>
+        <v>6686897</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7493,10 +7493,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123302252</v>
+        <v>123302241</v>
       </c>
       <c r="B62" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7533,10 +7533,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>404884</v>
+        <v>404765</v>
       </c>
       <c r="R62" t="n">
-        <v>6686940</v>
+        <v>6686893</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7595,10 +7595,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123302240</v>
+        <v>123302254</v>
       </c>
       <c r="B63" t="n">
-        <v>95911</v>
+        <v>95914</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7635,10 +7635,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>404906</v>
+        <v>404893</v>
       </c>
       <c r="R63" t="n">
-        <v>6686997</v>
+        <v>6687000</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7697,10 +7697,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123302243</v>
+        <v>123302264</v>
       </c>
       <c r="B64" t="n">
-        <v>82553</v>
+        <v>92271</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7713,21 +7713,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1312</v>
+        <v>5966</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7737,10 +7737,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>404663</v>
+        <v>405076</v>
       </c>
       <c r="R64" t="n">
-        <v>6686805</v>
+        <v>6687116</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7799,10 +7799,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>123302264</v>
+        <v>123302246</v>
       </c>
       <c r="B65" t="n">
-        <v>92268</v>
+        <v>78769</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7815,21 +7815,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5966</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7839,10 +7839,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>405076</v>
+        <v>404908</v>
       </c>
       <c r="R65" t="n">
-        <v>6687116</v>
+        <v>6687022</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7901,10 +7901,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>123302253</v>
+        <v>123302256</v>
       </c>
       <c r="B66" t="n">
-        <v>95911</v>
+        <v>92236</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7913,25 +7913,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>53</v>
+        <v>4364</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7941,10 +7941,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>404899</v>
+        <v>404740</v>
       </c>
       <c r="R66" t="n">
-        <v>6686991</v>
+        <v>6686779</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8003,10 +8003,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>123302262</v>
+        <v>123302257</v>
       </c>
       <c r="B67" t="n">
-        <v>78502</v>
+        <v>78769</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8019,21 +8019,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8043,10 +8043,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>404991</v>
+        <v>404825</v>
       </c>
       <c r="R67" t="n">
-        <v>6687033</v>
+        <v>6686922</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8105,10 +8105,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>123302246</v>
+        <v>123302237</v>
       </c>
       <c r="B68" t="n">
-        <v>78766</v>
+        <v>78505</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8121,21 +8121,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8145,10 +8145,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>404908</v>
+        <v>404784</v>
       </c>
       <c r="R68" t="n">
-        <v>6687022</v>
+        <v>6686893</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8207,10 +8207,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>123302251</v>
+        <v>123302249</v>
       </c>
       <c r="B69" t="n">
-        <v>78766</v>
+        <v>95914</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8223,21 +8223,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8247,10 +8247,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>404754</v>
+        <v>404925</v>
       </c>
       <c r="R69" t="n">
-        <v>6686824</v>
+        <v>6687022</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8309,10 +8309,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>123302234</v>
+        <v>123302253</v>
       </c>
       <c r="B70" t="n">
-        <v>78766</v>
+        <v>95914</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8325,21 +8325,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8349,10 +8349,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>404896</v>
+        <v>404899</v>
       </c>
       <c r="R70" t="n">
-        <v>6686928</v>
+        <v>6686991</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8411,10 +8411,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>123302249</v>
+        <v>123302248</v>
       </c>
       <c r="B71" t="n">
-        <v>95911</v>
+        <v>78769</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8427,21 +8427,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8451,10 +8451,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>404925</v>
+        <v>404485</v>
       </c>
       <c r="R71" t="n">
-        <v>6687022</v>
+        <v>6686609</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>

--- a/artfynd/A 6315-2025 artfynd.xlsx
+++ b/artfynd/A 6315-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY71"/>
+  <dimension ref="A1:AY79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4888,10 +4888,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123025268</v>
+        <v>123025288</v>
       </c>
       <c r="B37" t="n">
-        <v>78769</v>
+        <v>78508</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4904,26 +4904,26 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J37" t="inlineStr"/>
@@ -4931,14 +4931,14 @@
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Svarttjärnen 4, Vimyrens naturreservat, Vrm</t>
+          <t>Svarttjärnen 5, Vimyrens naturreservat, Vrm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>404828</v>
+        <v>404846</v>
       </c>
       <c r="R37" t="n">
-        <v>6686867</v>
+        <v>6686878</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4998,10 +4998,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123024336</v>
+        <v>123024872</v>
       </c>
       <c r="B38" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5041,14 +5041,14 @@
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Svarttjärnen 1, Vimyrens naturreservat, Vrm</t>
+          <t>Svarttjärnen 2, Vimyrens naturreservat, Vrm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>404722</v>
+        <v>404740</v>
       </c>
       <c r="R38" t="n">
-        <v>6686761</v>
+        <v>6686776</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5108,10 +5108,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123025288</v>
+        <v>123024336</v>
       </c>
       <c r="B39" t="n">
-        <v>78506</v>
+        <v>78771</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5124,21 +5124,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -5151,14 +5151,14 @@
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Svarttjärnen 5, Vimyrens naturreservat, Vrm</t>
+          <t>Svarttjärnen 1, Vimyrens naturreservat, Vrm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>404846</v>
+        <v>404722</v>
       </c>
       <c r="R39" t="n">
-        <v>6686878</v>
+        <v>6686761</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5218,10 +5218,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123024872</v>
+        <v>123025268</v>
       </c>
       <c r="B40" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5253,7 +5253,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J40" t="inlineStr"/>
@@ -5261,14 +5261,14 @@
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Svarttjärnen 2, Vimyrens naturreservat, Vrm</t>
+          <t>Svarttjärnen 4, Vimyrens naturreservat, Vrm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>404740</v>
+        <v>404828</v>
       </c>
       <c r="R40" t="n">
-        <v>6686776</v>
+        <v>6686867</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5328,10 +5328,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123025220</v>
+        <v>123025199</v>
       </c>
       <c r="B41" t="n">
-        <v>95914</v>
+        <v>95034</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5340,25 +5340,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>53</v>
+        <v>2170</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -5414,11 +5414,6 @@
           <t>2025-03-07</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>En låga med riklig förekomst på</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5444,10 +5439,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123025199</v>
+        <v>123025220</v>
       </c>
       <c r="B42" t="n">
-        <v>95032</v>
+        <v>95916</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5456,25 +5451,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2170</v>
+        <v>53</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -5530,6 +5525,11 @@
           <t>2025-03-07</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>En låga med riklig förekomst på</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5555,10 +5555,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123302247</v>
+        <v>123302258</v>
       </c>
       <c r="B43" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>404900</v>
+        <v>404812</v>
       </c>
       <c r="R43" t="n">
-        <v>6686936</v>
+        <v>6686926</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5657,10 +5657,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123302240</v>
+        <v>123302263</v>
       </c>
       <c r="B44" t="n">
-        <v>95914</v>
+        <v>78771</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5673,21 +5673,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5697,10 +5697,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>404906</v>
+        <v>405174</v>
       </c>
       <c r="R44" t="n">
-        <v>6686997</v>
+        <v>6687209</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5759,10 +5759,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123302238</v>
+        <v>123302244</v>
       </c>
       <c r="B45" t="n">
-        <v>92236</v>
+        <v>78771</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5771,25 +5771,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5799,10 +5799,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>404664</v>
+        <v>404831</v>
       </c>
       <c r="R45" t="n">
-        <v>6686821</v>
+        <v>6686961</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5861,10 +5861,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123302251</v>
+        <v>123302253</v>
       </c>
       <c r="B46" t="n">
-        <v>78769</v>
+        <v>95916</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5877,21 +5877,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5901,10 +5901,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>404754</v>
+        <v>404899</v>
       </c>
       <c r="R46" t="n">
-        <v>6686824</v>
+        <v>6686991</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5963,10 +5963,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123302259</v>
+        <v>123302254</v>
       </c>
       <c r="B47" t="n">
-        <v>78769</v>
+        <v>95916</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5979,21 +5979,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -6003,10 +6003,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>404680</v>
+        <v>404893</v>
       </c>
       <c r="R47" t="n">
-        <v>6686815</v>
+        <v>6687000</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6065,10 +6065,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123302250</v>
+        <v>123302241</v>
       </c>
       <c r="B48" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6105,10 +6105,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>404749</v>
+        <v>404765</v>
       </c>
       <c r="R48" t="n">
-        <v>6686779</v>
+        <v>6686893</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6167,10 +6167,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123302258</v>
+        <v>123302234</v>
       </c>
       <c r="B49" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6207,10 +6207,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>404812</v>
+        <v>404896</v>
       </c>
       <c r="R49" t="n">
-        <v>6686926</v>
+        <v>6686928</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6269,10 +6269,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123302244</v>
+        <v>123302259</v>
       </c>
       <c r="B50" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6309,10 +6309,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>404831</v>
+        <v>404680</v>
       </c>
       <c r="R50" t="n">
-        <v>6686961</v>
+        <v>6686815</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6371,10 +6371,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123302234</v>
+        <v>123302252</v>
       </c>
       <c r="B51" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6411,10 +6411,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>404896</v>
+        <v>404884</v>
       </c>
       <c r="R51" t="n">
-        <v>6686928</v>
+        <v>6686940</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6473,10 +6473,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123302239</v>
+        <v>123302256</v>
       </c>
       <c r="B52" t="n">
-        <v>95914</v>
+        <v>92238</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6485,25 +6485,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>53</v>
+        <v>4364</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6513,10 +6513,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>404942</v>
+        <v>404740</v>
       </c>
       <c r="R52" t="n">
-        <v>6686972</v>
+        <v>6686779</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6575,10 +6575,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123302236</v>
+        <v>123302247</v>
       </c>
       <c r="B53" t="n">
-        <v>78506</v>
+        <v>78771</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6591,21 +6591,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6615,10 +6615,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>404784</v>
+        <v>404900</v>
       </c>
       <c r="R53" t="n">
-        <v>6686893</v>
+        <v>6686936</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6677,10 +6677,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123302242</v>
+        <v>123302261</v>
       </c>
       <c r="B54" t="n">
-        <v>78769</v>
+        <v>78508</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6693,21 +6693,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6717,10 +6717,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>404779</v>
+        <v>404755</v>
       </c>
       <c r="R54" t="n">
-        <v>6686907</v>
+        <v>6686809</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6779,10 +6779,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123302243</v>
+        <v>123302251</v>
       </c>
       <c r="B55" t="n">
-        <v>82556</v>
+        <v>78771</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6795,21 +6795,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6819,10 +6819,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>404663</v>
+        <v>404754</v>
       </c>
       <c r="R55" t="n">
-        <v>6686805</v>
+        <v>6686824</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6881,10 +6881,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123302261</v>
+        <v>123302243</v>
       </c>
       <c r="B56" t="n">
-        <v>78506</v>
+        <v>82558</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6897,21 +6897,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>228912</v>
+        <v>1312</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6921,10 +6921,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>404755</v>
+        <v>404663</v>
       </c>
       <c r="R56" t="n">
-        <v>6686809</v>
+        <v>6686805</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6983,10 +6983,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123302263</v>
+        <v>123302255</v>
       </c>
       <c r="B57" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7023,10 +7023,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>405174</v>
+        <v>404742</v>
       </c>
       <c r="R57" t="n">
-        <v>6687209</v>
+        <v>6686791</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7085,10 +7085,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123302255</v>
+        <v>123302264</v>
       </c>
       <c r="B58" t="n">
-        <v>78769</v>
+        <v>92273</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7101,21 +7101,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7125,10 +7125,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>404742</v>
+        <v>405076</v>
       </c>
       <c r="R58" t="n">
-        <v>6686791</v>
+        <v>6687116</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7190,7 +7190,7 @@
         <v>123302262</v>
       </c>
       <c r="B59" t="n">
-        <v>78505</v>
+        <v>78507</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7289,10 +7289,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123302252</v>
+        <v>123302238</v>
       </c>
       <c r="B60" t="n">
-        <v>78769</v>
+        <v>92238</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7301,25 +7301,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7329,10 +7329,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>404884</v>
+        <v>404664</v>
       </c>
       <c r="R60" t="n">
-        <v>6686940</v>
+        <v>6686821</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7391,10 +7391,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123302235</v>
+        <v>123302239</v>
       </c>
       <c r="B61" t="n">
-        <v>78769</v>
+        <v>95916</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7407,21 +7407,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7431,10 +7431,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>404825</v>
+        <v>404942</v>
       </c>
       <c r="R61" t="n">
-        <v>6686897</v>
+        <v>6686972</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7493,10 +7493,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123302241</v>
+        <v>123302237</v>
       </c>
       <c r="B62" t="n">
-        <v>78769</v>
+        <v>78507</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7509,21 +7509,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7533,7 +7533,7 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>404765</v>
+        <v>404784</v>
       </c>
       <c r="R62" t="n">
         <v>6686893</v>
@@ -7595,10 +7595,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123302254</v>
+        <v>123302250</v>
       </c>
       <c r="B63" t="n">
-        <v>95914</v>
+        <v>78771</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7611,21 +7611,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7635,10 +7635,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>404893</v>
+        <v>404749</v>
       </c>
       <c r="R63" t="n">
-        <v>6687000</v>
+        <v>6686779</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7697,10 +7697,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123302264</v>
+        <v>123302242</v>
       </c>
       <c r="B64" t="n">
-        <v>92271</v>
+        <v>78771</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7713,21 +7713,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5966</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7737,10 +7737,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>405076</v>
+        <v>404779</v>
       </c>
       <c r="R64" t="n">
-        <v>6687116</v>
+        <v>6686907</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7799,10 +7799,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>123302246</v>
+        <v>123302257</v>
       </c>
       <c r="B65" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7839,10 +7839,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>404908</v>
+        <v>404825</v>
       </c>
       <c r="R65" t="n">
-        <v>6687022</v>
+        <v>6686922</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7901,10 +7901,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>123302256</v>
+        <v>123302248</v>
       </c>
       <c r="B66" t="n">
-        <v>92236</v>
+        <v>78771</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7913,25 +7913,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7941,10 +7941,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>404740</v>
+        <v>404485</v>
       </c>
       <c r="R66" t="n">
-        <v>6686779</v>
+        <v>6686609</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8003,10 +8003,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>123302257</v>
+        <v>123302236</v>
       </c>
       <c r="B67" t="n">
-        <v>78769</v>
+        <v>78508</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8019,21 +8019,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8043,10 +8043,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>404825</v>
+        <v>404784</v>
       </c>
       <c r="R67" t="n">
-        <v>6686922</v>
+        <v>6686893</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8105,10 +8105,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>123302237</v>
+        <v>123302235</v>
       </c>
       <c r="B68" t="n">
-        <v>78505</v>
+        <v>78771</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8121,21 +8121,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8145,10 +8145,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>404784</v>
+        <v>404825</v>
       </c>
       <c r="R68" t="n">
-        <v>6686893</v>
+        <v>6686897</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8207,10 +8207,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>123302249</v>
+        <v>123302246</v>
       </c>
       <c r="B69" t="n">
-        <v>95914</v>
+        <v>78771</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8223,21 +8223,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8247,7 +8247,7 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>404925</v>
+        <v>404908</v>
       </c>
       <c r="R69" t="n">
         <v>6687022</v>
@@ -8309,10 +8309,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>123302253</v>
+        <v>123302240</v>
       </c>
       <c r="B70" t="n">
-        <v>95914</v>
+        <v>95916</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8349,10 +8349,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>404899</v>
+        <v>404906</v>
       </c>
       <c r="R70" t="n">
-        <v>6686991</v>
+        <v>6686997</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8411,10 +8411,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>123302248</v>
+        <v>123302249</v>
       </c>
       <c r="B71" t="n">
-        <v>78769</v>
+        <v>95916</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8427,21 +8427,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8451,10 +8451,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>404485</v>
+        <v>404925</v>
       </c>
       <c r="R71" t="n">
-        <v>6686609</v>
+        <v>6687022</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8510,6 +8510,854 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>123484017</v>
+      </c>
+      <c r="B72" t="n">
+        <v>78508</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Svarttjärnen 12, Vrm</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>404849</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6686889</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF72" t="inlineStr"/>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Sofia Damne</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Sofia Damne</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>123483891</v>
+      </c>
+      <c r="B73" t="n">
+        <v>78507</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Svarttjärnen 7, Vrm</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>404939</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6687011</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF73" t="inlineStr"/>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Sofia Damne</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Sofia Damne</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>123483876</v>
+      </c>
+      <c r="B74" t="n">
+        <v>78508</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Svarttjärnen 6, Vrm</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>404984</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6687077</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF74" t="inlineStr"/>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Sofia Damne</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Sofia Damne</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>123484000</v>
+      </c>
+      <c r="B75" t="n">
+        <v>78507</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Svarttjärnen 9, Vrm</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>404763</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6686809</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="inlineStr"/>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Sofia Damne</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Sofia Damne</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>123484009</v>
+      </c>
+      <c r="B76" t="n">
+        <v>78771</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Svarttjärnen 11, Vrm</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>404831</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6686875</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF76" t="inlineStr"/>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Sofia Damne</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Sofia Damne</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>123484005</v>
+      </c>
+      <c r="B77" t="n">
+        <v>78771</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Svarttjärnen 10, Vrm</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>404746</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6686832</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF77" t="inlineStr"/>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Sofia Damne</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Sofia Damne</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>123483987</v>
+      </c>
+      <c r="B78" t="n">
+        <v>78771</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Svarttjärnen 8, Vrm</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>404649</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6686758</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF78" t="inlineStr"/>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Sofia Damne</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Sofia Damne</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>123483866</v>
+      </c>
+      <c r="B79" t="n">
+        <v>78771</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Svarttjärnen 6, Vrm</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>404984</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6687077</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2025-03-12</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF79" t="inlineStr"/>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Sofia Damne</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Sofia Damne</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 6315-2025 artfynd.xlsx
+++ b/artfynd/A 6315-2025 artfynd.xlsx
@@ -5555,10 +5555,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123302258</v>
+        <v>123302253</v>
       </c>
       <c r="B43" t="n">
-        <v>78771</v>
+        <v>95916</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5571,21 +5571,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>404812</v>
+        <v>404899</v>
       </c>
       <c r="R43" t="n">
-        <v>6686926</v>
+        <v>6686991</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5657,10 +5657,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123302263</v>
+        <v>123302254</v>
       </c>
       <c r="B44" t="n">
-        <v>78771</v>
+        <v>95916</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5673,21 +5673,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5697,10 +5697,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>405174</v>
+        <v>404893</v>
       </c>
       <c r="R44" t="n">
-        <v>6687209</v>
+        <v>6687000</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5759,7 +5759,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123302244</v>
+        <v>123302258</v>
       </c>
       <c r="B45" t="n">
         <v>78771</v>
@@ -5799,10 +5799,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>404831</v>
+        <v>404812</v>
       </c>
       <c r="R45" t="n">
-        <v>6686961</v>
+        <v>6686926</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5861,10 +5861,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123302253</v>
+        <v>123302263</v>
       </c>
       <c r="B46" t="n">
-        <v>95916</v>
+        <v>78771</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5877,21 +5877,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5901,10 +5901,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>404899</v>
+        <v>405174</v>
       </c>
       <c r="R46" t="n">
-        <v>6686991</v>
+        <v>6687209</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5963,10 +5963,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123302254</v>
+        <v>123302244</v>
       </c>
       <c r="B47" t="n">
-        <v>95916</v>
+        <v>78771</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5979,21 +5979,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -6003,10 +6003,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>404893</v>
+        <v>404831</v>
       </c>
       <c r="R47" t="n">
-        <v>6687000</v>
+        <v>6686961</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -7187,10 +7187,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123302262</v>
+        <v>123302238</v>
       </c>
       <c r="B59" t="n">
-        <v>78507</v>
+        <v>92238</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7199,25 +7199,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7227,10 +7227,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>404991</v>
+        <v>404664</v>
       </c>
       <c r="R59" t="n">
-        <v>6687033</v>
+        <v>6686821</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7289,10 +7289,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123302238</v>
+        <v>123302262</v>
       </c>
       <c r="B60" t="n">
-        <v>92238</v>
+        <v>78507</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7301,25 +7301,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7329,10 +7329,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>404664</v>
+        <v>404991</v>
       </c>
       <c r="R60" t="n">
-        <v>6686821</v>
+        <v>6687033</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>

--- a/artfynd/A 6315-2025 artfynd.xlsx
+++ b/artfynd/A 6315-2025 artfynd.xlsx
@@ -4888,10 +4888,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123025288</v>
+        <v>123024336</v>
       </c>
       <c r="B37" t="n">
-        <v>78508</v>
+        <v>78772</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4904,21 +4904,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -4931,14 +4931,14 @@
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Svarttjärnen 5, Vimyrens naturreservat, Vrm</t>
+          <t>Svarttjärnen 1, Vimyrens naturreservat, Vrm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>404846</v>
+        <v>404722</v>
       </c>
       <c r="R37" t="n">
-        <v>6686878</v>
+        <v>6686761</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5001,7 +5001,7 @@
         <v>123024872</v>
       </c>
       <c r="B38" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5108,10 +5108,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123024336</v>
+        <v>123025288</v>
       </c>
       <c r="B39" t="n">
-        <v>78771</v>
+        <v>78509</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5124,21 +5124,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -5151,14 +5151,14 @@
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Svarttjärnen 1, Vimyrens naturreservat, Vrm</t>
+          <t>Svarttjärnen 5, Vimyrens naturreservat, Vrm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>404722</v>
+        <v>404846</v>
       </c>
       <c r="R39" t="n">
-        <v>6686761</v>
+        <v>6686878</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5221,7 +5221,7 @@
         <v>123025268</v>
       </c>
       <c r="B40" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5328,10 +5328,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123025199</v>
+        <v>123025220</v>
       </c>
       <c r="B41" t="n">
-        <v>95034</v>
+        <v>95922</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5340,25 +5340,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2170</v>
+        <v>53</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -5414,6 +5414,11 @@
           <t>2025-03-07</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>En låga med riklig förekomst på</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5439,10 +5444,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123025220</v>
+        <v>123025199</v>
       </c>
       <c r="B42" t="n">
-        <v>95916</v>
+        <v>95040</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5451,25 +5456,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>53</v>
+        <v>2170</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -5525,11 +5530,6 @@
           <t>2025-03-07</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>En låga med riklig förekomst på</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5555,10 +5555,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123302253</v>
+        <v>123302262</v>
       </c>
       <c r="B43" t="n">
-        <v>95916</v>
+        <v>78508</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5571,21 +5571,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>53</v>
+        <v>6446</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>404899</v>
+        <v>404991</v>
       </c>
       <c r="R43" t="n">
-        <v>6686991</v>
+        <v>6687033</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5657,10 +5657,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123302254</v>
+        <v>123302244</v>
       </c>
       <c r="B44" t="n">
-        <v>95916</v>
+        <v>78772</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5673,21 +5673,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5697,10 +5697,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>404893</v>
+        <v>404831</v>
       </c>
       <c r="R44" t="n">
-        <v>6687000</v>
+        <v>6686961</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5759,10 +5759,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123302258</v>
+        <v>123302236</v>
       </c>
       <c r="B45" t="n">
-        <v>78771</v>
+        <v>78509</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5775,21 +5775,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5799,10 +5799,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>404812</v>
+        <v>404784</v>
       </c>
       <c r="R45" t="n">
-        <v>6686926</v>
+        <v>6686893</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5861,10 +5861,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123302263</v>
+        <v>123302255</v>
       </c>
       <c r="B46" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5901,10 +5901,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>405174</v>
+        <v>404742</v>
       </c>
       <c r="R46" t="n">
-        <v>6687209</v>
+        <v>6686791</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5963,10 +5963,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123302244</v>
+        <v>123302263</v>
       </c>
       <c r="B47" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6003,10 +6003,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>404831</v>
+        <v>405174</v>
       </c>
       <c r="R47" t="n">
-        <v>6686961</v>
+        <v>6687209</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6065,10 +6065,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123302241</v>
+        <v>123302264</v>
       </c>
       <c r="B48" t="n">
-        <v>78771</v>
+        <v>92279</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6081,21 +6081,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6105,10 +6105,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>404765</v>
+        <v>405076</v>
       </c>
       <c r="R48" t="n">
-        <v>6686893</v>
+        <v>6687116</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6167,10 +6167,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123302234</v>
+        <v>123302241</v>
       </c>
       <c r="B49" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6207,10 +6207,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>404896</v>
+        <v>404765</v>
       </c>
       <c r="R49" t="n">
-        <v>6686928</v>
+        <v>6686893</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6269,10 +6269,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123302259</v>
+        <v>123302248</v>
       </c>
       <c r="B50" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6309,10 +6309,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>404680</v>
+        <v>404485</v>
       </c>
       <c r="R50" t="n">
-        <v>6686815</v>
+        <v>6686609</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6371,10 +6371,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123302252</v>
+        <v>123302261</v>
       </c>
       <c r="B51" t="n">
-        <v>78771</v>
+        <v>78509</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6387,21 +6387,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6411,10 +6411,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>404884</v>
+        <v>404755</v>
       </c>
       <c r="R51" t="n">
-        <v>6686940</v>
+        <v>6686809</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6473,10 +6473,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123302256</v>
+        <v>123302246</v>
       </c>
       <c r="B52" t="n">
-        <v>92238</v>
+        <v>78772</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6485,25 +6485,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6513,10 +6513,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>404740</v>
+        <v>404908</v>
       </c>
       <c r="R52" t="n">
-        <v>6686779</v>
+        <v>6687022</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6575,10 +6575,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123302247</v>
+        <v>123302239</v>
       </c>
       <c r="B53" t="n">
-        <v>78771</v>
+        <v>95922</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6591,21 +6591,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6615,10 +6615,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>404900</v>
+        <v>404942</v>
       </c>
       <c r="R53" t="n">
-        <v>6686936</v>
+        <v>6686972</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6677,10 +6677,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123302261</v>
+        <v>123302234</v>
       </c>
       <c r="B54" t="n">
-        <v>78508</v>
+        <v>78772</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6693,21 +6693,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6717,10 +6717,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>404755</v>
+        <v>404896</v>
       </c>
       <c r="R54" t="n">
-        <v>6686809</v>
+        <v>6686928</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6779,10 +6779,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123302251</v>
+        <v>123302257</v>
       </c>
       <c r="B55" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6819,10 +6819,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>404754</v>
+        <v>404825</v>
       </c>
       <c r="R55" t="n">
-        <v>6686824</v>
+        <v>6686922</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6881,10 +6881,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123302243</v>
+        <v>123302237</v>
       </c>
       <c r="B56" t="n">
-        <v>82558</v>
+        <v>78508</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6897,21 +6897,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1312</v>
+        <v>6446</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6921,10 +6921,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>404663</v>
+        <v>404784</v>
       </c>
       <c r="R56" t="n">
-        <v>6686805</v>
+        <v>6686893</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6983,10 +6983,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123302255</v>
+        <v>123302249</v>
       </c>
       <c r="B57" t="n">
-        <v>78771</v>
+        <v>95922</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6999,21 +6999,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7023,10 +7023,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>404742</v>
+        <v>404925</v>
       </c>
       <c r="R57" t="n">
-        <v>6686791</v>
+        <v>6687022</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7085,10 +7085,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123302264</v>
+        <v>123302247</v>
       </c>
       <c r="B58" t="n">
-        <v>92273</v>
+        <v>78772</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7101,21 +7101,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5966</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7125,10 +7125,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>405076</v>
+        <v>404900</v>
       </c>
       <c r="R58" t="n">
-        <v>6687116</v>
+        <v>6686936</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7187,10 +7187,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123302238</v>
+        <v>123302240</v>
       </c>
       <c r="B59" t="n">
-        <v>92238</v>
+        <v>95922</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7199,25 +7199,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4364</v>
+        <v>53</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7227,10 +7227,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>404664</v>
+        <v>404906</v>
       </c>
       <c r="R59" t="n">
-        <v>6686821</v>
+        <v>6686997</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7289,10 +7289,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123302262</v>
+        <v>123302238</v>
       </c>
       <c r="B60" t="n">
-        <v>78507</v>
+        <v>92244</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7301,25 +7301,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7329,10 +7329,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>404991</v>
+        <v>404664</v>
       </c>
       <c r="R60" t="n">
-        <v>6687033</v>
+        <v>6686821</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7391,10 +7391,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123302239</v>
+        <v>123302254</v>
       </c>
       <c r="B61" t="n">
-        <v>95916</v>
+        <v>95922</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7431,10 +7431,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>404942</v>
+        <v>404893</v>
       </c>
       <c r="R61" t="n">
-        <v>6686972</v>
+        <v>6687000</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7493,10 +7493,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123302237</v>
+        <v>123302252</v>
       </c>
       <c r="B62" t="n">
-        <v>78507</v>
+        <v>78772</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7509,21 +7509,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7533,10 +7533,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>404784</v>
+        <v>404884</v>
       </c>
       <c r="R62" t="n">
-        <v>6686893</v>
+        <v>6686940</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7595,10 +7595,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123302250</v>
+        <v>123302256</v>
       </c>
       <c r="B63" t="n">
-        <v>78771</v>
+        <v>92244</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7607,25 +7607,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7635,7 +7635,7 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>404749</v>
+        <v>404740</v>
       </c>
       <c r="R63" t="n">
         <v>6686779</v>
@@ -7697,10 +7697,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123302242</v>
+        <v>123302258</v>
       </c>
       <c r="B64" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7737,10 +7737,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>404779</v>
+        <v>404812</v>
       </c>
       <c r="R64" t="n">
-        <v>6686907</v>
+        <v>6686926</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7799,10 +7799,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>123302257</v>
+        <v>123302253</v>
       </c>
       <c r="B65" t="n">
-        <v>78771</v>
+        <v>95922</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7815,21 +7815,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7839,10 +7839,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>404825</v>
+        <v>404899</v>
       </c>
       <c r="R65" t="n">
-        <v>6686922</v>
+        <v>6686991</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7901,10 +7901,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>123302248</v>
+        <v>123302242</v>
       </c>
       <c r="B66" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7941,10 +7941,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>404485</v>
+        <v>404779</v>
       </c>
       <c r="R66" t="n">
-        <v>6686609</v>
+        <v>6686907</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8003,10 +8003,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>123302236</v>
+        <v>123302259</v>
       </c>
       <c r="B67" t="n">
-        <v>78508</v>
+        <v>78772</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8019,21 +8019,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8043,10 +8043,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>404784</v>
+        <v>404680</v>
       </c>
       <c r="R67" t="n">
-        <v>6686893</v>
+        <v>6686815</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8108,7 +8108,7 @@
         <v>123302235</v>
       </c>
       <c r="B68" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8207,10 +8207,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>123302246</v>
+        <v>123302251</v>
       </c>
       <c r="B69" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8247,10 +8247,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>404908</v>
+        <v>404754</v>
       </c>
       <c r="R69" t="n">
-        <v>6687022</v>
+        <v>6686824</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8309,10 +8309,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>123302240</v>
+        <v>123302250</v>
       </c>
       <c r="B70" t="n">
-        <v>95916</v>
+        <v>78772</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8325,21 +8325,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8349,10 +8349,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>404906</v>
+        <v>404749</v>
       </c>
       <c r="R70" t="n">
-        <v>6686997</v>
+        <v>6686779</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8411,10 +8411,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>123302249</v>
+        <v>123302243</v>
       </c>
       <c r="B71" t="n">
-        <v>95916</v>
+        <v>82559</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8427,21 +8427,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>53</v>
+        <v>1312</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8451,10 +8451,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>404925</v>
+        <v>404663</v>
       </c>
       <c r="R71" t="n">
-        <v>6687022</v>
+        <v>6686805</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8516,7 +8516,7 @@
         <v>123484017</v>
       </c>
       <c r="B72" t="n">
-        <v>78508</v>
+        <v>78509</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8619,10 +8619,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>123483891</v>
+        <v>123483866</v>
       </c>
       <c r="B73" t="n">
-        <v>78507</v>
+        <v>78772</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8635,21 +8635,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8658,14 +8658,14 @@
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Svarttjärnen 7, Vrm</t>
+          <t>Svarttjärnen 6, Vrm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>404939</v>
+        <v>404984</v>
       </c>
       <c r="R73" t="n">
-        <v>6687011</v>
+        <v>6687077</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8725,10 +8725,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>123483876</v>
+        <v>123483987</v>
       </c>
       <c r="B74" t="n">
-        <v>78508</v>
+        <v>78772</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8741,21 +8741,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8764,14 +8764,14 @@
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Svarttjärnen 6, Vrm</t>
+          <t>Svarttjärnen 8, Vrm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>404984</v>
+        <v>404649</v>
       </c>
       <c r="R74" t="n">
-        <v>6687077</v>
+        <v>6686758</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8831,10 +8831,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>123484000</v>
+        <v>123483876</v>
       </c>
       <c r="B75" t="n">
-        <v>78507</v>
+        <v>78509</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8847,21 +8847,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8870,14 +8870,14 @@
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Svarttjärnen 9, Vrm</t>
+          <t>Svarttjärnen 6, Vrm</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>404763</v>
+        <v>404984</v>
       </c>
       <c r="R75" t="n">
-        <v>6686809</v>
+        <v>6687077</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8937,10 +8937,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>123484009</v>
+        <v>123483891</v>
       </c>
       <c r="B76" t="n">
-        <v>78771</v>
+        <v>78508</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8953,21 +8953,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8976,14 +8976,14 @@
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Svarttjärnen 11, Vrm</t>
+          <t>Svarttjärnen 7, Vrm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>404831</v>
+        <v>404939</v>
       </c>
       <c r="R76" t="n">
-        <v>6686875</v>
+        <v>6687011</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9043,10 +9043,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>123484005</v>
+        <v>123484009</v>
       </c>
       <c r="B77" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9082,14 +9082,14 @@
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Svarttjärnen 10, Vrm</t>
+          <t>Svarttjärnen 11, Vrm</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>404746</v>
+        <v>404831</v>
       </c>
       <c r="R77" t="n">
-        <v>6686832</v>
+        <v>6686875</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9149,10 +9149,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>123483987</v>
+        <v>123484000</v>
       </c>
       <c r="B78" t="n">
-        <v>78771</v>
+        <v>78508</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9165,21 +9165,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9188,14 +9188,14 @@
       <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Svarttjärnen 8, Vrm</t>
+          <t>Svarttjärnen 9, Vrm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>404649</v>
+        <v>404763</v>
       </c>
       <c r="R78" t="n">
-        <v>6686758</v>
+        <v>6686809</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9255,10 +9255,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>123483866</v>
+        <v>123484005</v>
       </c>
       <c r="B79" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9294,14 +9294,14 @@
       <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Svarttjärnen 6, Vrm</t>
+          <t>Svarttjärnen 10, Vrm</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>404984</v>
+        <v>404746</v>
       </c>
       <c r="R79" t="n">
-        <v>6687077</v>
+        <v>6686832</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>

--- a/artfynd/A 6315-2025 artfynd.xlsx
+++ b/artfynd/A 6315-2025 artfynd.xlsx
@@ -4888,10 +4888,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123025268</v>
+        <v>123024336</v>
       </c>
       <c r="B37" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J37" t="inlineStr"/>
@@ -4931,14 +4931,14 @@
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Svarttjärnen 4, Vimyrens naturreservat, Vrm</t>
+          <t>Svarttjärnen 1, Vimyrens naturreservat, Vrm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>404828</v>
+        <v>404722</v>
       </c>
       <c r="R37" t="n">
-        <v>6686867</v>
+        <v>6686761</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4998,10 +4998,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123024872</v>
+        <v>123025268</v>
       </c>
       <c r="B38" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5033,7 +5033,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J38" t="inlineStr"/>
@@ -5041,14 +5041,14 @@
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Svarttjärnen 2, Vimyrens naturreservat, Vrm</t>
+          <t>Svarttjärnen 4, Vimyrens naturreservat, Vrm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>404740</v>
+        <v>404828</v>
       </c>
       <c r="R38" t="n">
-        <v>6686776</v>
+        <v>6686867</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5111,7 +5111,7 @@
         <v>123025288</v>
       </c>
       <c r="B39" t="n">
-        <v>78512</v>
+        <v>78518</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5218,10 +5218,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123024336</v>
+        <v>123024872</v>
       </c>
       <c r="B40" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5261,14 +5261,14 @@
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Svarttjärnen 1, Vimyrens naturreservat, Vrm</t>
+          <t>Svarttjärnen 2, Vimyrens naturreservat, Vrm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>404722</v>
+        <v>404740</v>
       </c>
       <c r="R40" t="n">
-        <v>6686761</v>
+        <v>6686776</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5331,7 +5331,7 @@
         <v>123025220</v>
       </c>
       <c r="B41" t="n">
-        <v>95925</v>
+        <v>95942</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5447,7 +5447,7 @@
         <v>123025199</v>
       </c>
       <c r="B42" t="n">
-        <v>95043</v>
+        <v>95060</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5558,7 +5558,7 @@
         <v>123302250</v>
       </c>
       <c r="B43" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5657,10 +5657,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123302263</v>
+        <v>123302243</v>
       </c>
       <c r="B44" t="n">
-        <v>78775</v>
+        <v>82568</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5673,21 +5673,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5697,10 +5697,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>405174</v>
+        <v>404663</v>
       </c>
       <c r="R44" t="n">
-        <v>6687209</v>
+        <v>6686805</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5759,10 +5759,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123302264</v>
+        <v>123302236</v>
       </c>
       <c r="B45" t="n">
-        <v>92282</v>
+        <v>78518</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5775,21 +5775,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5966</v>
+        <v>228912</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5799,10 +5799,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>405076</v>
+        <v>404784</v>
       </c>
       <c r="R45" t="n">
-        <v>6687116</v>
+        <v>6686893</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5861,10 +5861,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123302261</v>
+        <v>123302247</v>
       </c>
       <c r="B46" t="n">
-        <v>78512</v>
+        <v>78781</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5877,21 +5877,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5901,10 +5901,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>404755</v>
+        <v>404900</v>
       </c>
       <c r="R46" t="n">
-        <v>6686809</v>
+        <v>6686936</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5963,10 +5963,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123302258</v>
+        <v>123302237</v>
       </c>
       <c r="B47" t="n">
-        <v>78775</v>
+        <v>78517</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5979,21 +5979,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -6003,10 +6003,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>404812</v>
+        <v>404784</v>
       </c>
       <c r="R47" t="n">
-        <v>6686926</v>
+        <v>6686893</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6065,10 +6065,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123302259</v>
+        <v>123302257</v>
       </c>
       <c r="B48" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6105,10 +6105,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>404680</v>
+        <v>404825</v>
       </c>
       <c r="R48" t="n">
-        <v>6686815</v>
+        <v>6686922</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6167,10 +6167,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123302243</v>
+        <v>123302263</v>
       </c>
       <c r="B49" t="n">
-        <v>82562</v>
+        <v>78781</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6183,21 +6183,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6207,10 +6207,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>404663</v>
+        <v>405174</v>
       </c>
       <c r="R49" t="n">
-        <v>6686805</v>
+        <v>6687209</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6269,10 +6269,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123302237</v>
+        <v>123302241</v>
       </c>
       <c r="B50" t="n">
-        <v>78511</v>
+        <v>78781</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6285,21 +6285,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6309,7 +6309,7 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>404784</v>
+        <v>404765</v>
       </c>
       <c r="R50" t="n">
         <v>6686893</v>
@@ -6371,10 +6371,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123302235</v>
+        <v>123302252</v>
       </c>
       <c r="B51" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6411,10 +6411,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>404825</v>
+        <v>404884</v>
       </c>
       <c r="R51" t="n">
-        <v>6686897</v>
+        <v>6686940</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6473,10 +6473,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123302239</v>
+        <v>123302251</v>
       </c>
       <c r="B52" t="n">
-        <v>95925</v>
+        <v>78781</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6489,21 +6489,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6513,10 +6513,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>404942</v>
+        <v>404754</v>
       </c>
       <c r="R52" t="n">
-        <v>6686972</v>
+        <v>6686824</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6575,10 +6575,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123302253</v>
+        <v>123302249</v>
       </c>
       <c r="B53" t="n">
-        <v>95925</v>
+        <v>95942</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6615,10 +6615,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>404899</v>
+        <v>404925</v>
       </c>
       <c r="R53" t="n">
-        <v>6686991</v>
+        <v>6687022</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6677,10 +6677,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123302257</v>
+        <v>123302262</v>
       </c>
       <c r="B54" t="n">
-        <v>78775</v>
+        <v>78517</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6693,21 +6693,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6717,10 +6717,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>404825</v>
+        <v>404991</v>
       </c>
       <c r="R54" t="n">
-        <v>6686922</v>
+        <v>6687033</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6779,10 +6779,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123302256</v>
+        <v>123302254</v>
       </c>
       <c r="B55" t="n">
-        <v>92247</v>
+        <v>95942</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6791,25 +6791,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4364</v>
+        <v>53</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6819,10 +6819,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>404740</v>
+        <v>404893</v>
       </c>
       <c r="R55" t="n">
-        <v>6686779</v>
+        <v>6687000</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6881,10 +6881,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123302248</v>
+        <v>123302238</v>
       </c>
       <c r="B56" t="n">
-        <v>78775</v>
+        <v>92264</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6893,25 +6893,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6921,10 +6921,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>404485</v>
+        <v>404664</v>
       </c>
       <c r="R56" t="n">
-        <v>6686609</v>
+        <v>6686821</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6983,10 +6983,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123302251</v>
+        <v>123302239</v>
       </c>
       <c r="B57" t="n">
-        <v>78775</v>
+        <v>95942</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6999,21 +6999,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7023,10 +7023,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>404754</v>
+        <v>404942</v>
       </c>
       <c r="R57" t="n">
-        <v>6686824</v>
+        <v>6686972</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7085,10 +7085,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123302236</v>
+        <v>123302264</v>
       </c>
       <c r="B58" t="n">
-        <v>78512</v>
+        <v>92299</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7101,21 +7101,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>228912</v>
+        <v>5966</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7125,10 +7125,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>404784</v>
+        <v>405076</v>
       </c>
       <c r="R58" t="n">
-        <v>6686893</v>
+        <v>6687116</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7187,10 +7187,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123302255</v>
+        <v>123302235</v>
       </c>
       <c r="B59" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7227,10 +7227,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>404742</v>
+        <v>404825</v>
       </c>
       <c r="R59" t="n">
-        <v>6686791</v>
+        <v>6686897</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7289,10 +7289,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123302242</v>
+        <v>123302261</v>
       </c>
       <c r="B60" t="n">
-        <v>78775</v>
+        <v>78518</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7305,21 +7305,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7329,10 +7329,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>404779</v>
+        <v>404755</v>
       </c>
       <c r="R60" t="n">
-        <v>6686907</v>
+        <v>6686809</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7391,10 +7391,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123302238</v>
+        <v>123302253</v>
       </c>
       <c r="B61" t="n">
-        <v>92247</v>
+        <v>95942</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7403,25 +7403,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4364</v>
+        <v>53</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7431,10 +7431,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>404664</v>
+        <v>404899</v>
       </c>
       <c r="R61" t="n">
-        <v>6686821</v>
+        <v>6686991</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7493,10 +7493,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123302254</v>
+        <v>123302258</v>
       </c>
       <c r="B62" t="n">
-        <v>95925</v>
+        <v>78781</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7509,21 +7509,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7533,10 +7533,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>404893</v>
+        <v>404812</v>
       </c>
       <c r="R62" t="n">
-        <v>6687000</v>
+        <v>6686926</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7595,10 +7595,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123302252</v>
+        <v>123302240</v>
       </c>
       <c r="B63" t="n">
-        <v>78775</v>
+        <v>95942</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7611,21 +7611,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7635,10 +7635,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>404884</v>
+        <v>404906</v>
       </c>
       <c r="R63" t="n">
-        <v>6686940</v>
+        <v>6686997</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7697,10 +7697,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123302240</v>
+        <v>123302256</v>
       </c>
       <c r="B64" t="n">
-        <v>95925</v>
+        <v>92264</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7709,25 +7709,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>53</v>
+        <v>4364</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7737,10 +7737,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>404906</v>
+        <v>404740</v>
       </c>
       <c r="R64" t="n">
-        <v>6686997</v>
+        <v>6686779</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7799,10 +7799,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>123302247</v>
+        <v>123302242</v>
       </c>
       <c r="B65" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7839,10 +7839,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>404900</v>
+        <v>404779</v>
       </c>
       <c r="R65" t="n">
-        <v>6686936</v>
+        <v>6686907</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7904,7 +7904,7 @@
         <v>123302244</v>
       </c>
       <c r="B66" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8003,10 +8003,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>123302262</v>
+        <v>123302248</v>
       </c>
       <c r="B67" t="n">
-        <v>78511</v>
+        <v>78781</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8019,21 +8019,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8043,10 +8043,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>404991</v>
+        <v>404485</v>
       </c>
       <c r="R67" t="n">
-        <v>6687033</v>
+        <v>6686609</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8105,10 +8105,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>123302246</v>
+        <v>123302255</v>
       </c>
       <c r="B68" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8145,10 +8145,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>404908</v>
+        <v>404742</v>
       </c>
       <c r="R68" t="n">
-        <v>6687022</v>
+        <v>6686791</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8207,10 +8207,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>123302249</v>
+        <v>123302259</v>
       </c>
       <c r="B69" t="n">
-        <v>95925</v>
+        <v>78781</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8223,21 +8223,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8247,10 +8247,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>404925</v>
+        <v>404680</v>
       </c>
       <c r="R69" t="n">
-        <v>6687022</v>
+        <v>6686815</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8309,10 +8309,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>123302234</v>
+        <v>123302246</v>
       </c>
       <c r="B70" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8349,10 +8349,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>404896</v>
+        <v>404908</v>
       </c>
       <c r="R70" t="n">
-        <v>6686928</v>
+        <v>6687022</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8411,10 +8411,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>123302241</v>
+        <v>123302234</v>
       </c>
       <c r="B71" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8451,10 +8451,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>404765</v>
+        <v>404896</v>
       </c>
       <c r="R71" t="n">
-        <v>6686893</v>
+        <v>6686928</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8513,10 +8513,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>123483876</v>
+        <v>123484017</v>
       </c>
       <c r="B72" t="n">
-        <v>78512</v>
+        <v>78518</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8552,14 +8552,14 @@
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Svarttjärnen 6, Vrm</t>
+          <t>Svarttjärnen 12, Vrm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>404984</v>
+        <v>404849</v>
       </c>
       <c r="R72" t="n">
-        <v>6687077</v>
+        <v>6686889</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8619,10 +8619,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>123484000</v>
+        <v>123484005</v>
       </c>
       <c r="B73" t="n">
-        <v>78511</v>
+        <v>78781</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8635,21 +8635,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8658,14 +8658,14 @@
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Svarttjärnen 9, Vrm</t>
+          <t>Svarttjärnen 10, Vrm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>404763</v>
+        <v>404746</v>
       </c>
       <c r="R73" t="n">
-        <v>6686809</v>
+        <v>6686832</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8725,10 +8725,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>123484005</v>
+        <v>123483876</v>
       </c>
       <c r="B74" t="n">
-        <v>78775</v>
+        <v>78518</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8741,21 +8741,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8764,14 +8764,14 @@
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Svarttjärnen 10, Vrm</t>
+          <t>Svarttjärnen 6, Vrm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>404746</v>
+        <v>404984</v>
       </c>
       <c r="R74" t="n">
-        <v>6686832</v>
+        <v>6687077</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8831,10 +8831,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>123483987</v>
+        <v>123483891</v>
       </c>
       <c r="B75" t="n">
-        <v>78775</v>
+        <v>78517</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8847,21 +8847,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8870,14 +8870,14 @@
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Svarttjärnen 8, Vrm</t>
+          <t>Svarttjärnen 7, Vrm</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>404649</v>
+        <v>404939</v>
       </c>
       <c r="R75" t="n">
-        <v>6686758</v>
+        <v>6687011</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8937,10 +8937,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>123484017</v>
+        <v>123483866</v>
       </c>
       <c r="B76" t="n">
-        <v>78512</v>
+        <v>78781</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8953,21 +8953,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8976,14 +8976,14 @@
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Svarttjärnen 12, Vrm</t>
+          <t>Svarttjärnen 6, Vrm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>404849</v>
+        <v>404984</v>
       </c>
       <c r="R76" t="n">
-        <v>6686889</v>
+        <v>6687077</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9043,10 +9043,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>123484009</v>
+        <v>123484000</v>
       </c>
       <c r="B77" t="n">
-        <v>78775</v>
+        <v>78517</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9059,21 +9059,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9082,14 +9082,14 @@
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Svarttjärnen 11, Vrm</t>
+          <t>Svarttjärnen 9, Vrm</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>404831</v>
+        <v>404763</v>
       </c>
       <c r="R77" t="n">
-        <v>6686875</v>
+        <v>6686809</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9149,10 +9149,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>123483866</v>
+        <v>123483987</v>
       </c>
       <c r="B78" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9188,14 +9188,14 @@
       <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Svarttjärnen 6, Vrm</t>
+          <t>Svarttjärnen 8, Vrm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>404984</v>
+        <v>404649</v>
       </c>
       <c r="R78" t="n">
-        <v>6687077</v>
+        <v>6686758</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9255,10 +9255,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>123483891</v>
+        <v>123484009</v>
       </c>
       <c r="B79" t="n">
-        <v>78511</v>
+        <v>78781</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9271,21 +9271,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9294,14 +9294,14 @@
       <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Svarttjärnen 7, Vrm</t>
+          <t>Svarttjärnen 11, Vrm</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>404939</v>
+        <v>404831</v>
       </c>
       <c r="R79" t="n">
-        <v>6687011</v>
+        <v>6686875</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>

--- a/artfynd/A 6315-2025 artfynd.xlsx
+++ b/artfynd/A 6315-2025 artfynd.xlsx
@@ -4998,10 +4998,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123025268</v>
+        <v>123025288</v>
       </c>
       <c r="B38" t="n">
-        <v>78781</v>
+        <v>78518</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5014,26 +5014,26 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J38" t="inlineStr"/>
@@ -5041,14 +5041,14 @@
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Svarttjärnen 4, Vimyrens naturreservat, Vrm</t>
+          <t>Svarttjärnen 5, Vimyrens naturreservat, Vrm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>404828</v>
+        <v>404846</v>
       </c>
       <c r="R38" t="n">
-        <v>6686867</v>
+        <v>6686878</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5108,10 +5108,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123025288</v>
+        <v>123025268</v>
       </c>
       <c r="B39" t="n">
-        <v>78518</v>
+        <v>78781</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5124,26 +5124,26 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J39" t="inlineStr"/>
@@ -5151,14 +5151,14 @@
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Svarttjärnen 5, Vimyrens naturreservat, Vrm</t>
+          <t>Svarttjärnen 4, Vimyrens naturreservat, Vrm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>404846</v>
+        <v>404828</v>
       </c>
       <c r="R39" t="n">
-        <v>6686878</v>
+        <v>6686867</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>

--- a/artfynd/A 6315-2025 artfynd.xlsx
+++ b/artfynd/A 6315-2025 artfynd.xlsx
@@ -4998,10 +4998,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123025288</v>
+        <v>123025268</v>
       </c>
       <c r="B38" t="n">
-        <v>78518</v>
+        <v>78781</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5014,26 +5014,26 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J38" t="inlineStr"/>
@@ -5041,14 +5041,14 @@
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Svarttjärnen 5, Vimyrens naturreservat, Vrm</t>
+          <t>Svarttjärnen 4, Vimyrens naturreservat, Vrm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>404846</v>
+        <v>404828</v>
       </c>
       <c r="R38" t="n">
-        <v>6686878</v>
+        <v>6686867</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5108,10 +5108,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123025268</v>
+        <v>123025288</v>
       </c>
       <c r="B39" t="n">
-        <v>78781</v>
+        <v>78518</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5124,26 +5124,26 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J39" t="inlineStr"/>
@@ -5151,14 +5151,14 @@
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Svarttjärnen 4, Vimyrens naturreservat, Vrm</t>
+          <t>Svarttjärnen 5, Vimyrens naturreservat, Vrm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>404828</v>
+        <v>404846</v>
       </c>
       <c r="R39" t="n">
-        <v>6686867</v>
+        <v>6686878</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>

--- a/artfynd/A 6315-2025 artfynd.xlsx
+++ b/artfynd/A 6315-2025 artfynd.xlsx
@@ -5328,10 +5328,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123025220</v>
+        <v>123025199</v>
       </c>
       <c r="B41" t="n">
-        <v>95942</v>
+        <v>95066</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5340,25 +5340,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>53</v>
+        <v>2170</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -5414,11 +5414,6 @@
           <t>2025-03-07</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>En låga med riklig förekomst på</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5444,10 +5439,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123025199</v>
+        <v>123025220</v>
       </c>
       <c r="B42" t="n">
-        <v>95060</v>
+        <v>95949</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5456,25 +5451,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2170</v>
+        <v>53</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -5530,6 +5525,11 @@
           <t>2025-03-07</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>En låga med riklig förekomst på</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5555,10 +5555,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123302250</v>
+        <v>123302249</v>
       </c>
       <c r="B43" t="n">
-        <v>78781</v>
+        <v>95949</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5571,21 +5571,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>404749</v>
+        <v>404925</v>
       </c>
       <c r="R43" t="n">
-        <v>6686779</v>
+        <v>6687022</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5657,10 +5657,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123302243</v>
+        <v>123302246</v>
       </c>
       <c r="B44" t="n">
-        <v>82568</v>
+        <v>78786</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5673,21 +5673,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5697,10 +5697,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>404663</v>
+        <v>404908</v>
       </c>
       <c r="R44" t="n">
-        <v>6686805</v>
+        <v>6687022</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5759,10 +5759,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123302236</v>
+        <v>123302256</v>
       </c>
       <c r="B45" t="n">
-        <v>78518</v>
+        <v>92269</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5771,25 +5771,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5799,10 +5799,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>404784</v>
+        <v>404740</v>
       </c>
       <c r="R45" t="n">
-        <v>6686893</v>
+        <v>6686779</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5861,10 +5861,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123302247</v>
+        <v>123302262</v>
       </c>
       <c r="B46" t="n">
-        <v>78781</v>
+        <v>78522</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5877,21 +5877,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5901,10 +5901,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>404900</v>
+        <v>404991</v>
       </c>
       <c r="R46" t="n">
-        <v>6686936</v>
+        <v>6687033</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5963,10 +5963,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123302237</v>
+        <v>123302254</v>
       </c>
       <c r="B47" t="n">
-        <v>78517</v>
+        <v>95949</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5979,21 +5979,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6446</v>
+        <v>53</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -6003,10 +6003,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>404784</v>
+        <v>404893</v>
       </c>
       <c r="R47" t="n">
-        <v>6686893</v>
+        <v>6687000</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6065,10 +6065,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123302257</v>
+        <v>123302242</v>
       </c>
       <c r="B48" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6105,10 +6105,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>404825</v>
+        <v>404779</v>
       </c>
       <c r="R48" t="n">
-        <v>6686922</v>
+        <v>6686907</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6167,10 +6167,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123302263</v>
+        <v>123302240</v>
       </c>
       <c r="B49" t="n">
-        <v>78781</v>
+        <v>95949</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6183,21 +6183,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6207,10 +6207,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>405174</v>
+        <v>404906</v>
       </c>
       <c r="R49" t="n">
-        <v>6687209</v>
+        <v>6686997</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6269,10 +6269,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123302241</v>
+        <v>123302257</v>
       </c>
       <c r="B50" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6309,10 +6309,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>404765</v>
+        <v>404825</v>
       </c>
       <c r="R50" t="n">
-        <v>6686893</v>
+        <v>6686922</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6371,10 +6371,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123302252</v>
+        <v>123302238</v>
       </c>
       <c r="B51" t="n">
-        <v>78781</v>
+        <v>92269</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6383,25 +6383,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6411,10 +6411,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>404884</v>
+        <v>404664</v>
       </c>
       <c r="R51" t="n">
-        <v>6686940</v>
+        <v>6686821</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6473,10 +6473,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123302251</v>
+        <v>123302234</v>
       </c>
       <c r="B52" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6513,10 +6513,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>404754</v>
+        <v>404896</v>
       </c>
       <c r="R52" t="n">
-        <v>6686824</v>
+        <v>6686928</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6575,10 +6575,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123302249</v>
+        <v>123302239</v>
       </c>
       <c r="B53" t="n">
-        <v>95942</v>
+        <v>95949</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6615,10 +6615,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>404925</v>
+        <v>404942</v>
       </c>
       <c r="R53" t="n">
-        <v>6687022</v>
+        <v>6686972</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6677,10 +6677,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123302262</v>
+        <v>123302237</v>
       </c>
       <c r="B54" t="n">
-        <v>78517</v>
+        <v>78522</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6717,10 +6717,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>404991</v>
+        <v>404784</v>
       </c>
       <c r="R54" t="n">
-        <v>6687033</v>
+        <v>6686893</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6779,10 +6779,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123302254</v>
+        <v>123302235</v>
       </c>
       <c r="B55" t="n">
-        <v>95942</v>
+        <v>78786</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6795,21 +6795,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6819,10 +6819,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>404893</v>
+        <v>404825</v>
       </c>
       <c r="R55" t="n">
-        <v>6687000</v>
+        <v>6686897</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6881,10 +6881,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123302238</v>
+        <v>123302255</v>
       </c>
       <c r="B56" t="n">
-        <v>92264</v>
+        <v>78786</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6893,25 +6893,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6921,10 +6921,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>404664</v>
+        <v>404742</v>
       </c>
       <c r="R56" t="n">
-        <v>6686821</v>
+        <v>6686791</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6983,10 +6983,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123302239</v>
+        <v>123302243</v>
       </c>
       <c r="B57" t="n">
-        <v>95942</v>
+        <v>82573</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6999,21 +6999,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>53</v>
+        <v>1312</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7023,10 +7023,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>404942</v>
+        <v>404663</v>
       </c>
       <c r="R57" t="n">
-        <v>6686972</v>
+        <v>6686805</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7085,10 +7085,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123302264</v>
+        <v>123302248</v>
       </c>
       <c r="B58" t="n">
-        <v>92299</v>
+        <v>78786</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7101,21 +7101,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5966</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7125,10 +7125,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>405076</v>
+        <v>404485</v>
       </c>
       <c r="R58" t="n">
-        <v>6687116</v>
+        <v>6686609</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7187,10 +7187,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123302235</v>
+        <v>123302264</v>
       </c>
       <c r="B59" t="n">
-        <v>78781</v>
+        <v>92304</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7203,21 +7203,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7227,10 +7227,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>404825</v>
+        <v>405076</v>
       </c>
       <c r="R59" t="n">
-        <v>6686897</v>
+        <v>6687116</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7289,10 +7289,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123302261</v>
+        <v>123302258</v>
       </c>
       <c r="B60" t="n">
-        <v>78518</v>
+        <v>78786</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7305,21 +7305,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7329,10 +7329,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>404755</v>
+        <v>404812</v>
       </c>
       <c r="R60" t="n">
-        <v>6686809</v>
+        <v>6686926</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7391,10 +7391,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123302253</v>
+        <v>123302261</v>
       </c>
       <c r="B61" t="n">
-        <v>95942</v>
+        <v>78523</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7407,21 +7407,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>53</v>
+        <v>228912</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7431,10 +7431,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>404899</v>
+        <v>404755</v>
       </c>
       <c r="R61" t="n">
-        <v>6686991</v>
+        <v>6686809</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7493,10 +7493,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123302258</v>
+        <v>123302259</v>
       </c>
       <c r="B62" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7533,10 +7533,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>404812</v>
+        <v>404680</v>
       </c>
       <c r="R62" t="n">
-        <v>6686926</v>
+        <v>6686815</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7595,10 +7595,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123302240</v>
+        <v>123302241</v>
       </c>
       <c r="B63" t="n">
-        <v>95942</v>
+        <v>78786</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7611,21 +7611,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7635,10 +7635,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>404906</v>
+        <v>404765</v>
       </c>
       <c r="R63" t="n">
-        <v>6686997</v>
+        <v>6686893</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7697,10 +7697,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123302256</v>
+        <v>123302250</v>
       </c>
       <c r="B64" t="n">
-        <v>92264</v>
+        <v>78786</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7709,25 +7709,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7737,7 +7737,7 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>404740</v>
+        <v>404749</v>
       </c>
       <c r="R64" t="n">
         <v>6686779</v>
@@ -7799,10 +7799,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>123302242</v>
+        <v>123302247</v>
       </c>
       <c r="B65" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7839,10 +7839,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>404779</v>
+        <v>404900</v>
       </c>
       <c r="R65" t="n">
-        <v>6686907</v>
+        <v>6686936</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7901,10 +7901,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>123302244</v>
+        <v>123302263</v>
       </c>
       <c r="B66" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7941,10 +7941,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>404831</v>
+        <v>405174</v>
       </c>
       <c r="R66" t="n">
-        <v>6686961</v>
+        <v>6687209</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8003,10 +8003,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>123302248</v>
+        <v>123302253</v>
       </c>
       <c r="B67" t="n">
-        <v>78781</v>
+        <v>95949</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8019,21 +8019,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8043,10 +8043,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>404485</v>
+        <v>404899</v>
       </c>
       <c r="R67" t="n">
-        <v>6686609</v>
+        <v>6686991</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8105,10 +8105,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>123302255</v>
+        <v>123302251</v>
       </c>
       <c r="B68" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8145,10 +8145,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>404742</v>
+        <v>404754</v>
       </c>
       <c r="R68" t="n">
-        <v>6686791</v>
+        <v>6686824</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8207,10 +8207,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>123302259</v>
+        <v>123302236</v>
       </c>
       <c r="B69" t="n">
-        <v>78781</v>
+        <v>78523</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8223,21 +8223,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8247,10 +8247,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>404680</v>
+        <v>404784</v>
       </c>
       <c r="R69" t="n">
-        <v>6686815</v>
+        <v>6686893</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8309,10 +8309,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>123302246</v>
+        <v>123302244</v>
       </c>
       <c r="B70" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8349,10 +8349,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>404908</v>
+        <v>404831</v>
       </c>
       <c r="R70" t="n">
-        <v>6687022</v>
+        <v>6686961</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8411,10 +8411,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>123302234</v>
+        <v>123302252</v>
       </c>
       <c r="B71" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8451,10 +8451,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>404896</v>
+        <v>404884</v>
       </c>
       <c r="R71" t="n">
-        <v>6686928</v>
+        <v>6686940</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8513,10 +8513,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>123484017</v>
+        <v>123483866</v>
       </c>
       <c r="B72" t="n">
-        <v>78518</v>
+        <v>78786</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8529,21 +8529,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8552,14 +8552,14 @@
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Svarttjärnen 12, Vrm</t>
+          <t>Svarttjärnen 6, Vrm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>404849</v>
+        <v>404984</v>
       </c>
       <c r="R72" t="n">
-        <v>6686889</v>
+        <v>6687077</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8619,10 +8619,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>123484005</v>
+        <v>123483891</v>
       </c>
       <c r="B73" t="n">
-        <v>78781</v>
+        <v>78522</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8635,21 +8635,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8658,14 +8658,14 @@
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Svarttjärnen 10, Vrm</t>
+          <t>Svarttjärnen 7, Vrm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>404746</v>
+        <v>404939</v>
       </c>
       <c r="R73" t="n">
-        <v>6686832</v>
+        <v>6687011</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8725,10 +8725,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>123483876</v>
+        <v>123484017</v>
       </c>
       <c r="B74" t="n">
-        <v>78518</v>
+        <v>78523</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8764,14 +8764,14 @@
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Svarttjärnen 6, Vrm</t>
+          <t>Svarttjärnen 12, Vrm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>404984</v>
+        <v>404849</v>
       </c>
       <c r="R74" t="n">
-        <v>6687077</v>
+        <v>6686889</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8831,10 +8831,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>123483891</v>
+        <v>123484005</v>
       </c>
       <c r="B75" t="n">
-        <v>78517</v>
+        <v>78786</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8847,21 +8847,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8870,14 +8870,14 @@
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Svarttjärnen 7, Vrm</t>
+          <t>Svarttjärnen 10, Vrm</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>404939</v>
+        <v>404746</v>
       </c>
       <c r="R75" t="n">
-        <v>6687011</v>
+        <v>6686832</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8937,10 +8937,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>123483866</v>
+        <v>123483987</v>
       </c>
       <c r="B76" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8976,14 +8976,14 @@
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Svarttjärnen 6, Vrm</t>
+          <t>Svarttjärnen 8, Vrm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>404984</v>
+        <v>404649</v>
       </c>
       <c r="R76" t="n">
-        <v>6687077</v>
+        <v>6686758</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9043,10 +9043,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>123484000</v>
+        <v>123484009</v>
       </c>
       <c r="B77" t="n">
-        <v>78517</v>
+        <v>78786</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9059,21 +9059,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9082,14 +9082,14 @@
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Svarttjärnen 9, Vrm</t>
+          <t>Svarttjärnen 11, Vrm</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>404763</v>
+        <v>404831</v>
       </c>
       <c r="R77" t="n">
-        <v>6686809</v>
+        <v>6686875</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9149,10 +9149,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>123483987</v>
+        <v>123483876</v>
       </c>
       <c r="B78" t="n">
-        <v>78781</v>
+        <v>78523</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9165,21 +9165,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9188,14 +9188,14 @@
       <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Svarttjärnen 8, Vrm</t>
+          <t>Svarttjärnen 6, Vrm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>404649</v>
+        <v>404984</v>
       </c>
       <c r="R78" t="n">
-        <v>6686758</v>
+        <v>6687077</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9255,10 +9255,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>123484009</v>
+        <v>123484000</v>
       </c>
       <c r="B79" t="n">
-        <v>78781</v>
+        <v>78522</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9271,21 +9271,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9294,14 +9294,14 @@
       <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Svarttjärnen 11, Vrm</t>
+          <t>Svarttjärnen 9, Vrm</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>404831</v>
+        <v>404763</v>
       </c>
       <c r="R79" t="n">
-        <v>6686875</v>
+        <v>6686809</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>

--- a/artfynd/A 6315-2025 artfynd.xlsx
+++ b/artfynd/A 6315-2025 artfynd.xlsx
@@ -5331,7 +5331,7 @@
         <v>123025199</v>
       </c>
       <c r="B41" t="n">
-        <v>95066</v>
+        <v>95068</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5442,7 +5442,7 @@
         <v>123025220</v>
       </c>
       <c r="B42" t="n">
-        <v>95949</v>
+        <v>95951</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5555,10 +5555,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123302249</v>
+        <v>123302240</v>
       </c>
       <c r="B43" t="n">
-        <v>95949</v>
+        <v>95951</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>404925</v>
+        <v>404906</v>
       </c>
       <c r="R43" t="n">
-        <v>6687022</v>
+        <v>6686997</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5657,10 +5657,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123302246</v>
+        <v>123302251</v>
       </c>
       <c r="B44" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5697,10 +5697,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>404908</v>
+        <v>404754</v>
       </c>
       <c r="R44" t="n">
-        <v>6687022</v>
+        <v>6686824</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5759,10 +5759,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123302256</v>
+        <v>123302246</v>
       </c>
       <c r="B45" t="n">
-        <v>92269</v>
+        <v>78788</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5771,25 +5771,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5799,10 +5799,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>404740</v>
+        <v>404908</v>
       </c>
       <c r="R45" t="n">
-        <v>6686779</v>
+        <v>6687022</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5861,10 +5861,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123302262</v>
+        <v>123302264</v>
       </c>
       <c r="B46" t="n">
-        <v>78522</v>
+        <v>92306</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5877,21 +5877,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6446</v>
+        <v>5966</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5901,10 +5901,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>404991</v>
+        <v>405076</v>
       </c>
       <c r="R46" t="n">
-        <v>6687033</v>
+        <v>6687116</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5963,10 +5963,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123302254</v>
+        <v>123302258</v>
       </c>
       <c r="B47" t="n">
-        <v>95949</v>
+        <v>78788</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5979,21 +5979,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -6003,10 +6003,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>404893</v>
+        <v>404812</v>
       </c>
       <c r="R47" t="n">
-        <v>6687000</v>
+        <v>6686926</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6065,10 +6065,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123302242</v>
+        <v>123302252</v>
       </c>
       <c r="B48" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6105,10 +6105,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>404779</v>
+        <v>404884</v>
       </c>
       <c r="R48" t="n">
-        <v>6686907</v>
+        <v>6686940</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6167,10 +6167,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123302240</v>
+        <v>123302259</v>
       </c>
       <c r="B49" t="n">
-        <v>95949</v>
+        <v>78788</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6183,21 +6183,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6207,10 +6207,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>404906</v>
+        <v>404680</v>
       </c>
       <c r="R49" t="n">
-        <v>6686997</v>
+        <v>6686815</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6269,10 +6269,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123302257</v>
+        <v>123302238</v>
       </c>
       <c r="B50" t="n">
-        <v>78786</v>
+        <v>92271</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6281,25 +6281,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6309,10 +6309,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>404825</v>
+        <v>404664</v>
       </c>
       <c r="R50" t="n">
-        <v>6686922</v>
+        <v>6686821</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6371,10 +6371,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123302238</v>
+        <v>123302257</v>
       </c>
       <c r="B51" t="n">
-        <v>92269</v>
+        <v>78788</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6383,25 +6383,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6411,10 +6411,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>404664</v>
+        <v>404825</v>
       </c>
       <c r="R51" t="n">
-        <v>6686821</v>
+        <v>6686922</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6473,10 +6473,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123302234</v>
+        <v>123302244</v>
       </c>
       <c r="B52" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6513,10 +6513,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>404896</v>
+        <v>404831</v>
       </c>
       <c r="R52" t="n">
-        <v>6686928</v>
+        <v>6686961</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6575,10 +6575,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123302239</v>
+        <v>123302236</v>
       </c>
       <c r="B53" t="n">
-        <v>95949</v>
+        <v>78525</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6591,21 +6591,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>53</v>
+        <v>228912</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6615,10 +6615,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>404942</v>
+        <v>404784</v>
       </c>
       <c r="R53" t="n">
-        <v>6686972</v>
+        <v>6686893</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6677,10 +6677,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123302237</v>
+        <v>123302241</v>
       </c>
       <c r="B54" t="n">
-        <v>78522</v>
+        <v>78788</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6693,21 +6693,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6717,7 +6717,7 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>404784</v>
+        <v>404765</v>
       </c>
       <c r="R54" t="n">
         <v>6686893</v>
@@ -6779,10 +6779,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123302235</v>
+        <v>123302243</v>
       </c>
       <c r="B55" t="n">
-        <v>78786</v>
+        <v>82575</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6795,21 +6795,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6819,10 +6819,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>404825</v>
+        <v>404663</v>
       </c>
       <c r="R55" t="n">
-        <v>6686897</v>
+        <v>6686805</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6881,10 +6881,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123302255</v>
+        <v>123302239</v>
       </c>
       <c r="B56" t="n">
-        <v>78786</v>
+        <v>95951</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6897,21 +6897,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6921,10 +6921,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>404742</v>
+        <v>404942</v>
       </c>
       <c r="R56" t="n">
-        <v>6686791</v>
+        <v>6686972</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6983,10 +6983,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123302243</v>
+        <v>123302248</v>
       </c>
       <c r="B57" t="n">
-        <v>82573</v>
+        <v>78788</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6999,21 +6999,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7023,10 +7023,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>404663</v>
+        <v>404485</v>
       </c>
       <c r="R57" t="n">
-        <v>6686805</v>
+        <v>6686609</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7085,10 +7085,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123302248</v>
+        <v>123302263</v>
       </c>
       <c r="B58" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7125,10 +7125,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>404485</v>
+        <v>405174</v>
       </c>
       <c r="R58" t="n">
-        <v>6686609</v>
+        <v>6687209</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7187,10 +7187,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123302264</v>
+        <v>123302253</v>
       </c>
       <c r="B59" t="n">
-        <v>92304</v>
+        <v>95951</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7203,21 +7203,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5966</v>
+        <v>53</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7227,10 +7227,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>405076</v>
+        <v>404899</v>
       </c>
       <c r="R59" t="n">
-        <v>6687116</v>
+        <v>6686991</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7289,10 +7289,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123302258</v>
+        <v>123302249</v>
       </c>
       <c r="B60" t="n">
-        <v>78786</v>
+        <v>95951</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7305,21 +7305,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7329,10 +7329,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>404812</v>
+        <v>404925</v>
       </c>
       <c r="R60" t="n">
-        <v>6686926</v>
+        <v>6687022</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7391,10 +7391,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123302261</v>
+        <v>123302234</v>
       </c>
       <c r="B61" t="n">
-        <v>78523</v>
+        <v>78788</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7407,21 +7407,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7431,10 +7431,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>404755</v>
+        <v>404896</v>
       </c>
       <c r="R61" t="n">
-        <v>6686809</v>
+        <v>6686928</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7493,10 +7493,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123302259</v>
+        <v>123302262</v>
       </c>
       <c r="B62" t="n">
-        <v>78786</v>
+        <v>78524</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7509,21 +7509,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7533,10 +7533,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>404680</v>
+        <v>404991</v>
       </c>
       <c r="R62" t="n">
-        <v>6686815</v>
+        <v>6687033</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7595,10 +7595,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123302241</v>
+        <v>123302256</v>
       </c>
       <c r="B63" t="n">
-        <v>78786</v>
+        <v>92271</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7607,25 +7607,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7635,10 +7635,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>404765</v>
+        <v>404740</v>
       </c>
       <c r="R63" t="n">
-        <v>6686893</v>
+        <v>6686779</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7697,10 +7697,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123302250</v>
+        <v>123302235</v>
       </c>
       <c r="B64" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7737,10 +7737,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>404749</v>
+        <v>404825</v>
       </c>
       <c r="R64" t="n">
-        <v>6686779</v>
+        <v>6686897</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7799,10 +7799,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>123302247</v>
+        <v>123302250</v>
       </c>
       <c r="B65" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7839,10 +7839,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>404900</v>
+        <v>404749</v>
       </c>
       <c r="R65" t="n">
-        <v>6686936</v>
+        <v>6686779</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7901,10 +7901,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>123302263</v>
+        <v>123302247</v>
       </c>
       <c r="B66" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7941,10 +7941,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>405174</v>
+        <v>404900</v>
       </c>
       <c r="R66" t="n">
-        <v>6687209</v>
+        <v>6686936</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8003,10 +8003,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>123302253</v>
+        <v>123302242</v>
       </c>
       <c r="B67" t="n">
-        <v>95949</v>
+        <v>78788</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8019,21 +8019,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8043,10 +8043,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>404899</v>
+        <v>404779</v>
       </c>
       <c r="R67" t="n">
-        <v>6686991</v>
+        <v>6686907</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8105,10 +8105,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>123302251</v>
+        <v>123302255</v>
       </c>
       <c r="B68" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8145,10 +8145,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>404754</v>
+        <v>404742</v>
       </c>
       <c r="R68" t="n">
-        <v>6686824</v>
+        <v>6686791</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8207,10 +8207,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>123302236</v>
+        <v>123302261</v>
       </c>
       <c r="B69" t="n">
-        <v>78523</v>
+        <v>78525</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8247,10 +8247,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>404784</v>
+        <v>404755</v>
       </c>
       <c r="R69" t="n">
-        <v>6686893</v>
+        <v>6686809</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8309,10 +8309,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>123302244</v>
+        <v>123302254</v>
       </c>
       <c r="B70" t="n">
-        <v>78786</v>
+        <v>95951</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8325,21 +8325,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8349,10 +8349,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>404831</v>
+        <v>404893</v>
       </c>
       <c r="R70" t="n">
-        <v>6686961</v>
+        <v>6687000</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8411,10 +8411,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>123302252</v>
+        <v>123302237</v>
       </c>
       <c r="B71" t="n">
-        <v>78786</v>
+        <v>78524</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8427,21 +8427,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8451,10 +8451,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>404884</v>
+        <v>404784</v>
       </c>
       <c r="R71" t="n">
-        <v>6686940</v>
+        <v>6686893</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8513,10 +8513,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>123483866</v>
+        <v>123483987</v>
       </c>
       <c r="B72" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8552,14 +8552,14 @@
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Svarttjärnen 6, Vrm</t>
+          <t>Svarttjärnen 8, Vrm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>404984</v>
+        <v>404649</v>
       </c>
       <c r="R72" t="n">
-        <v>6687077</v>
+        <v>6686758</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8619,10 +8619,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>123483891</v>
+        <v>123483866</v>
       </c>
       <c r="B73" t="n">
-        <v>78522</v>
+        <v>78788</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8635,21 +8635,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8658,14 +8658,14 @@
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Svarttjärnen 7, Vrm</t>
+          <t>Svarttjärnen 6, Vrm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>404939</v>
+        <v>404984</v>
       </c>
       <c r="R73" t="n">
-        <v>6687011</v>
+        <v>6687077</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8725,10 +8725,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>123484017</v>
+        <v>123484005</v>
       </c>
       <c r="B74" t="n">
-        <v>78523</v>
+        <v>78788</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8741,21 +8741,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8764,14 +8764,14 @@
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Svarttjärnen 12, Vrm</t>
+          <t>Svarttjärnen 10, Vrm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>404849</v>
+        <v>404746</v>
       </c>
       <c r="R74" t="n">
-        <v>6686889</v>
+        <v>6686832</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8831,10 +8831,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>123484005</v>
+        <v>123483876</v>
       </c>
       <c r="B75" t="n">
-        <v>78786</v>
+        <v>78525</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8847,21 +8847,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8870,14 +8870,14 @@
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Svarttjärnen 10, Vrm</t>
+          <t>Svarttjärnen 6, Vrm</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>404746</v>
+        <v>404984</v>
       </c>
       <c r="R75" t="n">
-        <v>6686832</v>
+        <v>6687077</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8937,10 +8937,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>123483987</v>
+        <v>123484009</v>
       </c>
       <c r="B76" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8976,14 +8976,14 @@
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Svarttjärnen 8, Vrm</t>
+          <t>Svarttjärnen 11, Vrm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>404649</v>
+        <v>404831</v>
       </c>
       <c r="R76" t="n">
-        <v>6686758</v>
+        <v>6686875</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9043,10 +9043,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>123484009</v>
+        <v>123484017</v>
       </c>
       <c r="B77" t="n">
-        <v>78786</v>
+        <v>78525</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9059,21 +9059,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9082,14 +9082,14 @@
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Svarttjärnen 11, Vrm</t>
+          <t>Svarttjärnen 12, Vrm</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>404831</v>
+        <v>404849</v>
       </c>
       <c r="R77" t="n">
-        <v>6686875</v>
+        <v>6686889</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9149,10 +9149,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>123483876</v>
+        <v>123483891</v>
       </c>
       <c r="B78" t="n">
-        <v>78523</v>
+        <v>78524</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9165,21 +9165,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9188,14 +9188,14 @@
       <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Svarttjärnen 6, Vrm</t>
+          <t>Svarttjärnen 7, Vrm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>404984</v>
+        <v>404939</v>
       </c>
       <c r="R78" t="n">
-        <v>6687077</v>
+        <v>6687011</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9258,7 +9258,7 @@
         <v>123484000</v>
       </c>
       <c r="B79" t="n">
-        <v>78522</v>
+        <v>78524</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>

--- a/artfynd/A 6315-2025 artfynd.xlsx
+++ b/artfynd/A 6315-2025 artfynd.xlsx
@@ -7289,10 +7289,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123302249</v>
+        <v>123302234</v>
       </c>
       <c r="B60" t="n">
-        <v>95951</v>
+        <v>78788</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7305,21 +7305,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7329,10 +7329,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>404925</v>
+        <v>404896</v>
       </c>
       <c r="R60" t="n">
-        <v>6687022</v>
+        <v>6686928</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7391,10 +7391,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123302234</v>
+        <v>123302262</v>
       </c>
       <c r="B61" t="n">
-        <v>78788</v>
+        <v>78524</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7407,21 +7407,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7431,10 +7431,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>404896</v>
+        <v>404991</v>
       </c>
       <c r="R61" t="n">
-        <v>6686928</v>
+        <v>6687033</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7493,10 +7493,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123302262</v>
+        <v>123302249</v>
       </c>
       <c r="B62" t="n">
-        <v>78524</v>
+        <v>95951</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7509,21 +7509,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6446</v>
+        <v>53</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7533,10 +7533,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>404991</v>
+        <v>404925</v>
       </c>
       <c r="R62" t="n">
-        <v>6687033</v>
+        <v>6687022</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>

--- a/artfynd/A 6315-2025 artfynd.xlsx
+++ b/artfynd/A 6315-2025 artfynd.xlsx
@@ -5555,10 +5555,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123302240</v>
+        <v>123302237</v>
       </c>
       <c r="B43" t="n">
-        <v>95951</v>
+        <v>78524</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5571,21 +5571,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>53</v>
+        <v>6446</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>404906</v>
+        <v>404784</v>
       </c>
       <c r="R43" t="n">
-        <v>6686997</v>
+        <v>6686893</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5657,7 +5657,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123302251</v>
+        <v>123302234</v>
       </c>
       <c r="B44" t="n">
         <v>78788</v>
@@ -5697,10 +5697,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>404754</v>
+        <v>404896</v>
       </c>
       <c r="R44" t="n">
-        <v>6686824</v>
+        <v>6686928</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5759,10 +5759,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123302246</v>
+        <v>123302243</v>
       </c>
       <c r="B45" t="n">
-        <v>78788</v>
+        <v>82575</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5775,21 +5775,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5799,10 +5799,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>404908</v>
+        <v>404663</v>
       </c>
       <c r="R45" t="n">
-        <v>6687022</v>
+        <v>6686805</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5861,10 +5861,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123302264</v>
+        <v>123302247</v>
       </c>
       <c r="B46" t="n">
-        <v>92306</v>
+        <v>78788</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5877,21 +5877,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5966</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5901,10 +5901,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>405076</v>
+        <v>404900</v>
       </c>
       <c r="R46" t="n">
-        <v>6687116</v>
+        <v>6686936</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5963,7 +5963,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123302258</v>
+        <v>123302251</v>
       </c>
       <c r="B47" t="n">
         <v>78788</v>
@@ -6003,10 +6003,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>404812</v>
+        <v>404754</v>
       </c>
       <c r="R47" t="n">
-        <v>6686926</v>
+        <v>6686824</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6065,10 +6065,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123302252</v>
+        <v>123302262</v>
       </c>
       <c r="B48" t="n">
-        <v>78788</v>
+        <v>78524</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6081,21 +6081,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6105,10 +6105,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>404884</v>
+        <v>404991</v>
       </c>
       <c r="R48" t="n">
-        <v>6686940</v>
+        <v>6687033</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6167,7 +6167,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123302259</v>
+        <v>123302246</v>
       </c>
       <c r="B49" t="n">
         <v>78788</v>
@@ -6207,10 +6207,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>404680</v>
+        <v>404908</v>
       </c>
       <c r="R49" t="n">
-        <v>6686815</v>
+        <v>6687022</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6269,10 +6269,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123302238</v>
+        <v>123302241</v>
       </c>
       <c r="B50" t="n">
-        <v>92271</v>
+        <v>78788</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6281,25 +6281,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6309,10 +6309,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>404664</v>
+        <v>404765</v>
       </c>
       <c r="R50" t="n">
-        <v>6686821</v>
+        <v>6686893</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6371,7 +6371,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123302257</v>
+        <v>123302255</v>
       </c>
       <c r="B51" t="n">
         <v>78788</v>
@@ -6411,10 +6411,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>404825</v>
+        <v>404742</v>
       </c>
       <c r="R51" t="n">
-        <v>6686922</v>
+        <v>6686791</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6473,7 +6473,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123302244</v>
+        <v>123302263</v>
       </c>
       <c r="B52" t="n">
         <v>78788</v>
@@ -6513,10 +6513,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>404831</v>
+        <v>405174</v>
       </c>
       <c r="R52" t="n">
-        <v>6686961</v>
+        <v>6687209</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6575,10 +6575,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123302236</v>
+        <v>123302252</v>
       </c>
       <c r="B53" t="n">
-        <v>78525</v>
+        <v>78788</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6591,21 +6591,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6615,10 +6615,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>404784</v>
+        <v>404884</v>
       </c>
       <c r="R53" t="n">
-        <v>6686893</v>
+        <v>6686940</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6677,10 +6677,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123302241</v>
+        <v>123302249</v>
       </c>
       <c r="B54" t="n">
-        <v>78788</v>
+        <v>96332</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6693,21 +6693,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6717,10 +6717,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>404765</v>
+        <v>404925</v>
       </c>
       <c r="R54" t="n">
-        <v>6686893</v>
+        <v>6687022</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6779,10 +6779,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123302243</v>
+        <v>123302240</v>
       </c>
       <c r="B55" t="n">
-        <v>82575</v>
+        <v>96332</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6795,21 +6795,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1312</v>
+        <v>53</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6819,10 +6819,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>404663</v>
+        <v>404906</v>
       </c>
       <c r="R55" t="n">
-        <v>6686805</v>
+        <v>6686997</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6881,10 +6881,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123302239</v>
+        <v>123302259</v>
       </c>
       <c r="B56" t="n">
-        <v>95951</v>
+        <v>78788</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6897,21 +6897,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6921,10 +6921,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>404942</v>
+        <v>404680</v>
       </c>
       <c r="R56" t="n">
-        <v>6686972</v>
+        <v>6686815</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6983,10 +6983,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123302248</v>
+        <v>123302236</v>
       </c>
       <c r="B57" t="n">
-        <v>78788</v>
+        <v>78525</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6999,21 +6999,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7023,10 +7023,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>404485</v>
+        <v>404784</v>
       </c>
       <c r="R57" t="n">
-        <v>6686609</v>
+        <v>6686893</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7085,7 +7085,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123302263</v>
+        <v>123302257</v>
       </c>
       <c r="B58" t="n">
         <v>78788</v>
@@ -7125,10 +7125,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>405174</v>
+        <v>404825</v>
       </c>
       <c r="R58" t="n">
-        <v>6687209</v>
+        <v>6686922</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7187,10 +7187,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123302253</v>
+        <v>123302248</v>
       </c>
       <c r="B59" t="n">
-        <v>95951</v>
+        <v>78788</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7203,21 +7203,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7227,10 +7227,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>404899</v>
+        <v>404485</v>
       </c>
       <c r="R59" t="n">
-        <v>6686991</v>
+        <v>6686609</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7289,10 +7289,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123302234</v>
+        <v>123302254</v>
       </c>
       <c r="B60" t="n">
-        <v>78788</v>
+        <v>96332</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7305,21 +7305,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7329,10 +7329,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>404896</v>
+        <v>404893</v>
       </c>
       <c r="R60" t="n">
-        <v>6686928</v>
+        <v>6687000</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7391,10 +7391,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123302262</v>
+        <v>123302238</v>
       </c>
       <c r="B61" t="n">
-        <v>78524</v>
+        <v>92271</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7403,25 +7403,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7431,10 +7431,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>404991</v>
+        <v>404664</v>
       </c>
       <c r="R61" t="n">
-        <v>6687033</v>
+        <v>6686821</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7493,10 +7493,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123302249</v>
+        <v>123302258</v>
       </c>
       <c r="B62" t="n">
-        <v>95951</v>
+        <v>78788</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7509,21 +7509,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7533,10 +7533,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>404925</v>
+        <v>404812</v>
       </c>
       <c r="R62" t="n">
-        <v>6687022</v>
+        <v>6686926</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7595,10 +7595,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123302256</v>
+        <v>123302264</v>
       </c>
       <c r="B63" t="n">
-        <v>92271</v>
+        <v>92306</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7607,25 +7607,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7635,10 +7635,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>404740</v>
+        <v>405076</v>
       </c>
       <c r="R63" t="n">
-        <v>6686779</v>
+        <v>6687116</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7697,7 +7697,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123302235</v>
+        <v>123302244</v>
       </c>
       <c r="B64" t="n">
         <v>78788</v>
@@ -7737,10 +7737,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>404825</v>
+        <v>404831</v>
       </c>
       <c r="R64" t="n">
-        <v>6686897</v>
+        <v>6686961</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7799,10 +7799,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>123302250</v>
+        <v>123302261</v>
       </c>
       <c r="B65" t="n">
-        <v>78788</v>
+        <v>78525</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7815,21 +7815,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7839,10 +7839,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>404749</v>
+        <v>404755</v>
       </c>
       <c r="R65" t="n">
-        <v>6686779</v>
+        <v>6686809</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7901,7 +7901,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>123302247</v>
+        <v>123302250</v>
       </c>
       <c r="B66" t="n">
         <v>78788</v>
@@ -7941,10 +7941,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>404900</v>
+        <v>404749</v>
       </c>
       <c r="R66" t="n">
-        <v>6686936</v>
+        <v>6686779</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8003,10 +8003,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>123302242</v>
+        <v>123302239</v>
       </c>
       <c r="B67" t="n">
-        <v>78788</v>
+        <v>96332</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8019,21 +8019,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8043,10 +8043,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>404779</v>
+        <v>404942</v>
       </c>
       <c r="R67" t="n">
-        <v>6686907</v>
+        <v>6686972</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8105,10 +8105,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>123302255</v>
+        <v>123302256</v>
       </c>
       <c r="B68" t="n">
-        <v>78788</v>
+        <v>92271</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8117,25 +8117,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8145,10 +8145,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>404742</v>
+        <v>404740</v>
       </c>
       <c r="R68" t="n">
-        <v>6686791</v>
+        <v>6686779</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8207,10 +8207,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>123302261</v>
+        <v>123302235</v>
       </c>
       <c r="B69" t="n">
-        <v>78525</v>
+        <v>78788</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8223,21 +8223,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8247,10 +8247,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>404755</v>
+        <v>404825</v>
       </c>
       <c r="R69" t="n">
-        <v>6686809</v>
+        <v>6686897</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8309,10 +8309,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>123302254</v>
+        <v>123302253</v>
       </c>
       <c r="B70" t="n">
-        <v>95951</v>
+        <v>96332</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8349,10 +8349,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>404893</v>
+        <v>404899</v>
       </c>
       <c r="R70" t="n">
-        <v>6687000</v>
+        <v>6686991</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8411,10 +8411,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>123302237</v>
+        <v>123302242</v>
       </c>
       <c r="B71" t="n">
-        <v>78524</v>
+        <v>78788</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8427,21 +8427,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8451,10 +8451,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>404784</v>
+        <v>404779</v>
       </c>
       <c r="R71" t="n">
-        <v>6686893</v>
+        <v>6686907</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8513,7 +8513,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>123483987</v>
+        <v>123484009</v>
       </c>
       <c r="B72" t="n">
         <v>78788</v>
@@ -8552,14 +8552,14 @@
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Svarttjärnen 8, Vrm</t>
+          <t>Svarttjärnen 11, Vrm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>404649</v>
+        <v>404831</v>
       </c>
       <c r="R72" t="n">
-        <v>6686758</v>
+        <v>6686875</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8619,10 +8619,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>123483866</v>
+        <v>123484000</v>
       </c>
       <c r="B73" t="n">
-        <v>78788</v>
+        <v>78524</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8635,21 +8635,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8658,14 +8658,14 @@
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Svarttjärnen 6, Vrm</t>
+          <t>Svarttjärnen 9, Vrm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>404984</v>
+        <v>404763</v>
       </c>
       <c r="R73" t="n">
-        <v>6687077</v>
+        <v>6686809</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8831,7 +8831,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>123483876</v>
+        <v>123484017</v>
       </c>
       <c r="B75" t="n">
         <v>78525</v>
@@ -8870,14 +8870,14 @@
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Svarttjärnen 6, Vrm</t>
+          <t>Svarttjärnen 12, Vrm</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>404984</v>
+        <v>404849</v>
       </c>
       <c r="R75" t="n">
-        <v>6687077</v>
+        <v>6686889</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8937,10 +8937,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>123484009</v>
+        <v>123483876</v>
       </c>
       <c r="B76" t="n">
-        <v>78788</v>
+        <v>78525</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8953,21 +8953,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8976,14 +8976,14 @@
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Svarttjärnen 11, Vrm</t>
+          <t>Svarttjärnen 6, Vrm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>404831</v>
+        <v>404984</v>
       </c>
       <c r="R76" t="n">
-        <v>6686875</v>
+        <v>6687077</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9043,10 +9043,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>123484017</v>
+        <v>123483987</v>
       </c>
       <c r="B77" t="n">
-        <v>78525</v>
+        <v>78788</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9059,21 +9059,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9082,14 +9082,14 @@
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Svarttjärnen 12, Vrm</t>
+          <t>Svarttjärnen 8, Vrm</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>404849</v>
+        <v>404649</v>
       </c>
       <c r="R77" t="n">
-        <v>6686889</v>
+        <v>6686758</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9149,10 +9149,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>123483891</v>
+        <v>123483866</v>
       </c>
       <c r="B78" t="n">
-        <v>78524</v>
+        <v>78788</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9165,21 +9165,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9188,14 +9188,14 @@
       <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Svarttjärnen 7, Vrm</t>
+          <t>Svarttjärnen 6, Vrm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>404939</v>
+        <v>404984</v>
       </c>
       <c r="R78" t="n">
-        <v>6687011</v>
+        <v>6687077</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9255,7 +9255,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>123484000</v>
+        <v>123483891</v>
       </c>
       <c r="B79" t="n">
         <v>78524</v>
@@ -9294,14 +9294,14 @@
       <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Svarttjärnen 9, Vrm</t>
+          <t>Svarttjärnen 7, Vrm</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>404763</v>
+        <v>404939</v>
       </c>
       <c r="R79" t="n">
-        <v>6686809</v>
+        <v>6687011</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>

--- a/artfynd/A 6315-2025 artfynd.xlsx
+++ b/artfynd/A 6315-2025 artfynd.xlsx
@@ -5555,10 +5555,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123302237</v>
+        <v>123302243</v>
       </c>
       <c r="B43" t="n">
-        <v>78524</v>
+        <v>82575</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5571,21 +5571,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6446</v>
+        <v>1312</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>404784</v>
+        <v>404663</v>
       </c>
       <c r="R43" t="n">
-        <v>6686893</v>
+        <v>6686805</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5657,10 +5657,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123302234</v>
+        <v>123302237</v>
       </c>
       <c r="B44" t="n">
-        <v>78788</v>
+        <v>78524</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5673,21 +5673,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5697,10 +5697,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>404896</v>
+        <v>404784</v>
       </c>
       <c r="R44" t="n">
-        <v>6686928</v>
+        <v>6686893</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5759,10 +5759,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123302243</v>
+        <v>123302234</v>
       </c>
       <c r="B45" t="n">
-        <v>82575</v>
+        <v>78788</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5775,21 +5775,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5799,10 +5799,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>404663</v>
+        <v>404896</v>
       </c>
       <c r="R45" t="n">
-        <v>6686805</v>
+        <v>6686928</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -7595,10 +7595,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123302264</v>
+        <v>123302261</v>
       </c>
       <c r="B63" t="n">
-        <v>92306</v>
+        <v>78525</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7611,21 +7611,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5966</v>
+        <v>228912</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7635,10 +7635,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>405076</v>
+        <v>404755</v>
       </c>
       <c r="R63" t="n">
-        <v>6687116</v>
+        <v>6686809</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7697,10 +7697,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123302244</v>
+        <v>123302264</v>
       </c>
       <c r="B64" t="n">
-        <v>78788</v>
+        <v>92306</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7713,21 +7713,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7737,10 +7737,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>404831</v>
+        <v>405076</v>
       </c>
       <c r="R64" t="n">
-        <v>6686961</v>
+        <v>6687116</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7799,10 +7799,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>123302261</v>
+        <v>123302244</v>
       </c>
       <c r="B65" t="n">
-        <v>78525</v>
+        <v>78788</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7815,21 +7815,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7839,10 +7839,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>404755</v>
+        <v>404831</v>
       </c>
       <c r="R65" t="n">
-        <v>6686809</v>
+        <v>6686961</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>

--- a/artfynd/A 6315-2025 artfynd.xlsx
+++ b/artfynd/A 6315-2025 artfynd.xlsx
@@ -5555,10 +5555,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123302243</v>
+        <v>123302263</v>
       </c>
       <c r="B43" t="n">
-        <v>82575</v>
+        <v>78788</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5571,21 +5571,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>404663</v>
+        <v>405174</v>
       </c>
       <c r="R43" t="n">
-        <v>6686805</v>
+        <v>6687209</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5657,10 +5657,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123302237</v>
+        <v>123302235</v>
       </c>
       <c r="B44" t="n">
-        <v>78524</v>
+        <v>78788</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5673,21 +5673,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5697,10 +5697,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>404784</v>
+        <v>404825</v>
       </c>
       <c r="R44" t="n">
-        <v>6686893</v>
+        <v>6686897</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5759,7 +5759,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123302234</v>
+        <v>123302242</v>
       </c>
       <c r="B45" t="n">
         <v>78788</v>
@@ -5799,10 +5799,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>404896</v>
+        <v>404779</v>
       </c>
       <c r="R45" t="n">
-        <v>6686928</v>
+        <v>6686907</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5861,10 +5861,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123302247</v>
+        <v>123302236</v>
       </c>
       <c r="B46" t="n">
-        <v>78788</v>
+        <v>78525</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5877,21 +5877,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5901,10 +5901,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>404900</v>
+        <v>404784</v>
       </c>
       <c r="R46" t="n">
-        <v>6686936</v>
+        <v>6686893</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5963,10 +5963,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123302251</v>
+        <v>123302240</v>
       </c>
       <c r="B47" t="n">
-        <v>78788</v>
+        <v>96332</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5979,21 +5979,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -6003,10 +6003,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>404754</v>
+        <v>404906</v>
       </c>
       <c r="R47" t="n">
-        <v>6686824</v>
+        <v>6686997</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6065,10 +6065,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123302262</v>
+        <v>123302247</v>
       </c>
       <c r="B48" t="n">
-        <v>78524</v>
+        <v>78788</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6081,21 +6081,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6105,10 +6105,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>404991</v>
+        <v>404900</v>
       </c>
       <c r="R48" t="n">
-        <v>6687033</v>
+        <v>6686936</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6167,7 +6167,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123302246</v>
+        <v>123302250</v>
       </c>
       <c r="B49" t="n">
         <v>78788</v>
@@ -6207,10 +6207,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>404908</v>
+        <v>404749</v>
       </c>
       <c r="R49" t="n">
-        <v>6687022</v>
+        <v>6686779</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6269,7 +6269,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123302241</v>
+        <v>123302234</v>
       </c>
       <c r="B50" t="n">
         <v>78788</v>
@@ -6309,10 +6309,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>404765</v>
+        <v>404896</v>
       </c>
       <c r="R50" t="n">
-        <v>6686893</v>
+        <v>6686928</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6371,10 +6371,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123302255</v>
+        <v>123302238</v>
       </c>
       <c r="B51" t="n">
-        <v>78788</v>
+        <v>92271</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6383,25 +6383,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6411,10 +6411,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>404742</v>
+        <v>404664</v>
       </c>
       <c r="R51" t="n">
-        <v>6686791</v>
+        <v>6686821</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6473,10 +6473,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123302263</v>
+        <v>123302254</v>
       </c>
       <c r="B52" t="n">
-        <v>78788</v>
+        <v>96332</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6489,21 +6489,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6513,10 +6513,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>405174</v>
+        <v>404893</v>
       </c>
       <c r="R52" t="n">
-        <v>6687209</v>
+        <v>6687000</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6575,7 +6575,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123302252</v>
+        <v>123302257</v>
       </c>
       <c r="B53" t="n">
         <v>78788</v>
@@ -6615,10 +6615,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>404884</v>
+        <v>404825</v>
       </c>
       <c r="R53" t="n">
-        <v>6686940</v>
+        <v>6686922</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6677,10 +6677,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123302249</v>
+        <v>123302251</v>
       </c>
       <c r="B54" t="n">
-        <v>96332</v>
+        <v>78788</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6693,21 +6693,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6717,10 +6717,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>404925</v>
+        <v>404754</v>
       </c>
       <c r="R54" t="n">
-        <v>6687022</v>
+        <v>6686824</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6779,7 +6779,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123302240</v>
+        <v>123302249</v>
       </c>
       <c r="B55" t="n">
         <v>96332</v>
@@ -6819,10 +6819,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>404906</v>
+        <v>404925</v>
       </c>
       <c r="R55" t="n">
-        <v>6686997</v>
+        <v>6687022</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6983,10 +6983,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123302236</v>
+        <v>123302256</v>
       </c>
       <c r="B57" t="n">
-        <v>78525</v>
+        <v>92271</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6995,25 +6995,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7023,10 +7023,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>404784</v>
+        <v>404740</v>
       </c>
       <c r="R57" t="n">
-        <v>6686893</v>
+        <v>6686779</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7085,7 +7085,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123302257</v>
+        <v>123302258</v>
       </c>
       <c r="B58" t="n">
         <v>78788</v>
@@ -7125,10 +7125,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>404825</v>
+        <v>404812</v>
       </c>
       <c r="R58" t="n">
-        <v>6686922</v>
+        <v>6686926</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7187,7 +7187,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123302248</v>
+        <v>123302255</v>
       </c>
       <c r="B59" t="n">
         <v>78788</v>
@@ -7227,10 +7227,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>404485</v>
+        <v>404742</v>
       </c>
       <c r="R59" t="n">
-        <v>6686609</v>
+        <v>6686791</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7289,10 +7289,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123302254</v>
+        <v>123302243</v>
       </c>
       <c r="B60" t="n">
-        <v>96332</v>
+        <v>82575</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7305,21 +7305,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>53</v>
+        <v>1312</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7329,10 +7329,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>404893</v>
+        <v>404663</v>
       </c>
       <c r="R60" t="n">
-        <v>6687000</v>
+        <v>6686805</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7391,10 +7391,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123302238</v>
+        <v>123302262</v>
       </c>
       <c r="B61" t="n">
-        <v>92271</v>
+        <v>78524</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7403,25 +7403,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7431,10 +7431,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>404664</v>
+        <v>404991</v>
       </c>
       <c r="R61" t="n">
-        <v>6686821</v>
+        <v>6687033</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7493,10 +7493,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123302258</v>
+        <v>123302237</v>
       </c>
       <c r="B62" t="n">
-        <v>78788</v>
+        <v>78524</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7509,21 +7509,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7533,10 +7533,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>404812</v>
+        <v>404784</v>
       </c>
       <c r="R62" t="n">
-        <v>6686926</v>
+        <v>6686893</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7595,10 +7595,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123302261</v>
+        <v>123302241</v>
       </c>
       <c r="B63" t="n">
-        <v>78525</v>
+        <v>78788</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7611,21 +7611,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7635,10 +7635,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>404755</v>
+        <v>404765</v>
       </c>
       <c r="R63" t="n">
-        <v>6686809</v>
+        <v>6686893</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7697,10 +7697,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123302264</v>
+        <v>123302261</v>
       </c>
       <c r="B64" t="n">
-        <v>92306</v>
+        <v>78525</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7713,21 +7713,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5966</v>
+        <v>228912</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7737,10 +7737,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>405076</v>
+        <v>404755</v>
       </c>
       <c r="R64" t="n">
-        <v>6687116</v>
+        <v>6686809</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7799,7 +7799,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>123302244</v>
+        <v>123302252</v>
       </c>
       <c r="B65" t="n">
         <v>78788</v>
@@ -7839,10 +7839,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>404831</v>
+        <v>404884</v>
       </c>
       <c r="R65" t="n">
-        <v>6686961</v>
+        <v>6686940</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7901,10 +7901,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>123302250</v>
+        <v>123302264</v>
       </c>
       <c r="B66" t="n">
-        <v>78788</v>
+        <v>92306</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7917,21 +7917,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7941,10 +7941,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>404749</v>
+        <v>405076</v>
       </c>
       <c r="R66" t="n">
-        <v>6686779</v>
+        <v>6687116</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8003,10 +8003,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>123302239</v>
+        <v>123302246</v>
       </c>
       <c r="B67" t="n">
-        <v>96332</v>
+        <v>78788</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8019,21 +8019,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8043,10 +8043,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>404942</v>
+        <v>404908</v>
       </c>
       <c r="R67" t="n">
-        <v>6686972</v>
+        <v>6687022</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8105,10 +8105,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>123302256</v>
+        <v>123302244</v>
       </c>
       <c r="B68" t="n">
-        <v>92271</v>
+        <v>78788</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8117,25 +8117,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8145,10 +8145,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>404740</v>
+        <v>404831</v>
       </c>
       <c r="R68" t="n">
-        <v>6686779</v>
+        <v>6686961</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8207,7 +8207,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>123302235</v>
+        <v>123302248</v>
       </c>
       <c r="B69" t="n">
         <v>78788</v>
@@ -8247,10 +8247,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>404825</v>
+        <v>404485</v>
       </c>
       <c r="R69" t="n">
-        <v>6686897</v>
+        <v>6686609</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8309,7 +8309,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>123302253</v>
+        <v>123302239</v>
       </c>
       <c r="B70" t="n">
         <v>96332</v>
@@ -8349,10 +8349,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>404899</v>
+        <v>404942</v>
       </c>
       <c r="R70" t="n">
-        <v>6686991</v>
+        <v>6686972</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8411,10 +8411,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>123302242</v>
+        <v>123302253</v>
       </c>
       <c r="B71" t="n">
-        <v>78788</v>
+        <v>96332</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8427,21 +8427,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8451,10 +8451,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>404779</v>
+        <v>404899</v>
       </c>
       <c r="R71" t="n">
-        <v>6686907</v>
+        <v>6686991</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8513,7 +8513,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>123484009</v>
+        <v>123484005</v>
       </c>
       <c r="B72" t="n">
         <v>78788</v>
@@ -8552,14 +8552,14 @@
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Svarttjärnen 11, Vrm</t>
+          <t>Svarttjärnen 10, Vrm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>404831</v>
+        <v>404746</v>
       </c>
       <c r="R72" t="n">
-        <v>6686875</v>
+        <v>6686832</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8619,10 +8619,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>123484000</v>
+        <v>123484017</v>
       </c>
       <c r="B73" t="n">
-        <v>78524</v>
+        <v>78525</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8635,21 +8635,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8658,14 +8658,14 @@
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Svarttjärnen 9, Vrm</t>
+          <t>Svarttjärnen 12, Vrm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>404763</v>
+        <v>404849</v>
       </c>
       <c r="R73" t="n">
-        <v>6686809</v>
+        <v>6686889</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8725,10 +8725,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>123484005</v>
+        <v>123483876</v>
       </c>
       <c r="B74" t="n">
-        <v>78788</v>
+        <v>78525</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8741,21 +8741,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8764,14 +8764,14 @@
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Svarttjärnen 10, Vrm</t>
+          <t>Svarttjärnen 6, Vrm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>404746</v>
+        <v>404984</v>
       </c>
       <c r="R74" t="n">
-        <v>6686832</v>
+        <v>6687077</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8831,10 +8831,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>123484017</v>
+        <v>123483866</v>
       </c>
       <c r="B75" t="n">
-        <v>78525</v>
+        <v>78788</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8847,21 +8847,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8870,14 +8870,14 @@
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Svarttjärnen 12, Vrm</t>
+          <t>Svarttjärnen 6, Vrm</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>404849</v>
+        <v>404984</v>
       </c>
       <c r="R75" t="n">
-        <v>6686889</v>
+        <v>6687077</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8937,10 +8937,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>123483876</v>
+        <v>123484000</v>
       </c>
       <c r="B76" t="n">
-        <v>78525</v>
+        <v>78524</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8953,21 +8953,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8976,14 +8976,14 @@
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Svarttjärnen 6, Vrm</t>
+          <t>Svarttjärnen 9, Vrm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>404984</v>
+        <v>404763</v>
       </c>
       <c r="R76" t="n">
-        <v>6687077</v>
+        <v>6686809</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9043,7 +9043,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>123483987</v>
+        <v>123484009</v>
       </c>
       <c r="B77" t="n">
         <v>78788</v>
@@ -9082,14 +9082,14 @@
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Svarttjärnen 8, Vrm</t>
+          <t>Svarttjärnen 11, Vrm</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>404649</v>
+        <v>404831</v>
       </c>
       <c r="R77" t="n">
-        <v>6686758</v>
+        <v>6686875</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9149,10 +9149,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>123483866</v>
+        <v>123483891</v>
       </c>
       <c r="B78" t="n">
-        <v>78788</v>
+        <v>78524</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9165,21 +9165,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9188,14 +9188,14 @@
       <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Svarttjärnen 6, Vrm</t>
+          <t>Svarttjärnen 7, Vrm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>404984</v>
+        <v>404939</v>
       </c>
       <c r="R78" t="n">
-        <v>6687077</v>
+        <v>6687011</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9255,10 +9255,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>123483891</v>
+        <v>123483987</v>
       </c>
       <c r="B79" t="n">
-        <v>78524</v>
+        <v>78788</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9271,21 +9271,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9294,14 +9294,14 @@
       <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Svarttjärnen 7, Vrm</t>
+          <t>Svarttjärnen 8, Vrm</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>404939</v>
+        <v>404649</v>
       </c>
       <c r="R79" t="n">
-        <v>6687011</v>
+        <v>6686758</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>

--- a/artfynd/A 6315-2025 artfynd.xlsx
+++ b/artfynd/A 6315-2025 artfynd.xlsx
@@ -5555,7 +5555,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123302263</v>
+        <v>123302244</v>
       </c>
       <c r="B43" t="n">
         <v>78788</v>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>405174</v>
+        <v>404831</v>
       </c>
       <c r="R43" t="n">
-        <v>6687209</v>
+        <v>6686961</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5657,7 +5657,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123302235</v>
+        <v>123302255</v>
       </c>
       <c r="B44" t="n">
         <v>78788</v>
@@ -5697,10 +5697,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>404825</v>
+        <v>404742</v>
       </c>
       <c r="R44" t="n">
-        <v>6686897</v>
+        <v>6686791</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5759,7 +5759,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123302242</v>
+        <v>123302234</v>
       </c>
       <c r="B45" t="n">
         <v>78788</v>
@@ -5799,10 +5799,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>404779</v>
+        <v>404896</v>
       </c>
       <c r="R45" t="n">
-        <v>6686907</v>
+        <v>6686928</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5861,10 +5861,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123302236</v>
+        <v>123302250</v>
       </c>
       <c r="B46" t="n">
-        <v>78525</v>
+        <v>78788</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5877,21 +5877,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5901,10 +5901,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>404784</v>
+        <v>404749</v>
       </c>
       <c r="R46" t="n">
-        <v>6686893</v>
+        <v>6686779</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5963,10 +5963,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123302240</v>
+        <v>123302261</v>
       </c>
       <c r="B47" t="n">
-        <v>96332</v>
+        <v>78525</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5979,21 +5979,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>53</v>
+        <v>228912</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -6003,10 +6003,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>404906</v>
+        <v>404755</v>
       </c>
       <c r="R47" t="n">
-        <v>6686997</v>
+        <v>6686809</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6065,10 +6065,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123302247</v>
+        <v>123302249</v>
       </c>
       <c r="B48" t="n">
-        <v>78788</v>
+        <v>96332</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6081,21 +6081,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6105,10 +6105,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>404900</v>
+        <v>404925</v>
       </c>
       <c r="R48" t="n">
-        <v>6686936</v>
+        <v>6687022</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6167,7 +6167,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123302250</v>
+        <v>123302251</v>
       </c>
       <c r="B49" t="n">
         <v>78788</v>
@@ -6207,10 +6207,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>404749</v>
+        <v>404754</v>
       </c>
       <c r="R49" t="n">
-        <v>6686779</v>
+        <v>6686824</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6269,10 +6269,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123302234</v>
+        <v>123302240</v>
       </c>
       <c r="B50" t="n">
-        <v>78788</v>
+        <v>96332</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6285,21 +6285,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6309,10 +6309,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>404896</v>
+        <v>404906</v>
       </c>
       <c r="R50" t="n">
-        <v>6686928</v>
+        <v>6686997</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6371,10 +6371,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123302238</v>
+        <v>123302263</v>
       </c>
       <c r="B51" t="n">
-        <v>92271</v>
+        <v>78788</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6383,25 +6383,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6411,10 +6411,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>404664</v>
+        <v>405174</v>
       </c>
       <c r="R51" t="n">
-        <v>6686821</v>
+        <v>6687209</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6473,10 +6473,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123302254</v>
+        <v>123302237</v>
       </c>
       <c r="B52" t="n">
-        <v>96332</v>
+        <v>78524</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6489,21 +6489,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>53</v>
+        <v>6446</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6513,10 +6513,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>404893</v>
+        <v>404784</v>
       </c>
       <c r="R52" t="n">
-        <v>6687000</v>
+        <v>6686893</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6575,10 +6575,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123302257</v>
+        <v>123302253</v>
       </c>
       <c r="B53" t="n">
-        <v>78788</v>
+        <v>96332</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6591,21 +6591,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6615,10 +6615,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>404825</v>
+        <v>404899</v>
       </c>
       <c r="R53" t="n">
-        <v>6686922</v>
+        <v>6686991</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6677,10 +6677,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123302251</v>
+        <v>123302256</v>
       </c>
       <c r="B54" t="n">
-        <v>78788</v>
+        <v>92271</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6689,25 +6689,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6717,10 +6717,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>404754</v>
+        <v>404740</v>
       </c>
       <c r="R54" t="n">
-        <v>6686824</v>
+        <v>6686779</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6779,10 +6779,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123302249</v>
+        <v>123302257</v>
       </c>
       <c r="B55" t="n">
-        <v>96332</v>
+        <v>78788</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6795,21 +6795,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6819,10 +6819,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>404925</v>
+        <v>404825</v>
       </c>
       <c r="R55" t="n">
-        <v>6687022</v>
+        <v>6686922</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6881,10 +6881,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123302259</v>
+        <v>123302262</v>
       </c>
       <c r="B56" t="n">
-        <v>78788</v>
+        <v>78524</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6897,21 +6897,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6921,10 +6921,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>404680</v>
+        <v>404991</v>
       </c>
       <c r="R56" t="n">
-        <v>6686815</v>
+        <v>6687033</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6983,10 +6983,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123302256</v>
+        <v>123302243</v>
       </c>
       <c r="B57" t="n">
-        <v>92271</v>
+        <v>82575</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6995,25 +6995,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4364</v>
+        <v>1312</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7023,10 +7023,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>404740</v>
+        <v>404663</v>
       </c>
       <c r="R57" t="n">
-        <v>6686779</v>
+        <v>6686805</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7085,7 +7085,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123302258</v>
+        <v>123302247</v>
       </c>
       <c r="B58" t="n">
         <v>78788</v>
@@ -7125,10 +7125,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>404812</v>
+        <v>404900</v>
       </c>
       <c r="R58" t="n">
-        <v>6686926</v>
+        <v>6686936</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7187,7 +7187,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123302255</v>
+        <v>123302241</v>
       </c>
       <c r="B59" t="n">
         <v>78788</v>
@@ -7227,10 +7227,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>404742</v>
+        <v>404765</v>
       </c>
       <c r="R59" t="n">
-        <v>6686791</v>
+        <v>6686893</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7289,10 +7289,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123302243</v>
+        <v>123302259</v>
       </c>
       <c r="B60" t="n">
-        <v>82575</v>
+        <v>78788</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7305,21 +7305,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7329,10 +7329,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>404663</v>
+        <v>404680</v>
       </c>
       <c r="R60" t="n">
-        <v>6686805</v>
+        <v>6686815</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7391,10 +7391,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123302262</v>
+        <v>123302238</v>
       </c>
       <c r="B61" t="n">
-        <v>78524</v>
+        <v>92271</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7403,25 +7403,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7431,10 +7431,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>404991</v>
+        <v>404664</v>
       </c>
       <c r="R61" t="n">
-        <v>6687033</v>
+        <v>6686821</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7493,10 +7493,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123302237</v>
+        <v>123302246</v>
       </c>
       <c r="B62" t="n">
-        <v>78524</v>
+        <v>78788</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7509,21 +7509,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7533,10 +7533,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>404784</v>
+        <v>404908</v>
       </c>
       <c r="R62" t="n">
-        <v>6686893</v>
+        <v>6687022</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7595,10 +7595,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123302241</v>
+        <v>123302239</v>
       </c>
       <c r="B63" t="n">
-        <v>78788</v>
+        <v>96332</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7611,21 +7611,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7635,10 +7635,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>404765</v>
+        <v>404942</v>
       </c>
       <c r="R63" t="n">
-        <v>6686893</v>
+        <v>6686972</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7697,10 +7697,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123302261</v>
+        <v>123302254</v>
       </c>
       <c r="B64" t="n">
-        <v>78525</v>
+        <v>96332</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7713,21 +7713,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>228912</v>
+        <v>53</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7737,10 +7737,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>404755</v>
+        <v>404893</v>
       </c>
       <c r="R64" t="n">
-        <v>6686809</v>
+        <v>6687000</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7799,7 +7799,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>123302252</v>
+        <v>123302242</v>
       </c>
       <c r="B65" t="n">
         <v>78788</v>
@@ -7839,10 +7839,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>404884</v>
+        <v>404779</v>
       </c>
       <c r="R65" t="n">
-        <v>6686940</v>
+        <v>6686907</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7901,10 +7901,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>123302264</v>
+        <v>123302248</v>
       </c>
       <c r="B66" t="n">
-        <v>92306</v>
+        <v>78788</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7917,21 +7917,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5966</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7941,10 +7941,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>405076</v>
+        <v>404485</v>
       </c>
       <c r="R66" t="n">
-        <v>6687116</v>
+        <v>6686609</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8003,7 +8003,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>123302246</v>
+        <v>123302258</v>
       </c>
       <c r="B67" t="n">
         <v>78788</v>
@@ -8043,10 +8043,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>404908</v>
+        <v>404812</v>
       </c>
       <c r="R67" t="n">
-        <v>6687022</v>
+        <v>6686926</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8105,7 +8105,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>123302244</v>
+        <v>123302252</v>
       </c>
       <c r="B68" t="n">
         <v>78788</v>
@@ -8145,10 +8145,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>404831</v>
+        <v>404884</v>
       </c>
       <c r="R68" t="n">
-        <v>6686961</v>
+        <v>6686940</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8207,10 +8207,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>123302248</v>
+        <v>123302236</v>
       </c>
       <c r="B69" t="n">
-        <v>78788</v>
+        <v>78525</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8223,21 +8223,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8247,10 +8247,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>404485</v>
+        <v>404784</v>
       </c>
       <c r="R69" t="n">
-        <v>6686609</v>
+        <v>6686893</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8309,10 +8309,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>123302239</v>
+        <v>123302235</v>
       </c>
       <c r="B70" t="n">
-        <v>96332</v>
+        <v>78788</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8325,21 +8325,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8349,10 +8349,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>404942</v>
+        <v>404825</v>
       </c>
       <c r="R70" t="n">
-        <v>6686972</v>
+        <v>6686897</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8411,10 +8411,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>123302253</v>
+        <v>123302264</v>
       </c>
       <c r="B71" t="n">
-        <v>96332</v>
+        <v>92306</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8427,21 +8427,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>53</v>
+        <v>5966</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8451,10 +8451,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>404899</v>
+        <v>405076</v>
       </c>
       <c r="R71" t="n">
-        <v>6686991</v>
+        <v>6687116</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8513,7 +8513,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>123484005</v>
+        <v>123483866</v>
       </c>
       <c r="B72" t="n">
         <v>78788</v>
@@ -8552,14 +8552,14 @@
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Svarttjärnen 10, Vrm</t>
+          <t>Svarttjärnen 6, Vrm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>404746</v>
+        <v>404984</v>
       </c>
       <c r="R72" t="n">
-        <v>6686832</v>
+        <v>6687077</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8619,7 +8619,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>123484017</v>
+        <v>123483876</v>
       </c>
       <c r="B73" t="n">
         <v>78525</v>
@@ -8658,14 +8658,14 @@
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Svarttjärnen 12, Vrm</t>
+          <t>Svarttjärnen 6, Vrm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>404849</v>
+        <v>404984</v>
       </c>
       <c r="R73" t="n">
-        <v>6686889</v>
+        <v>6687077</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8725,10 +8725,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>123483876</v>
+        <v>123484009</v>
       </c>
       <c r="B74" t="n">
-        <v>78525</v>
+        <v>78788</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8741,21 +8741,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8764,14 +8764,14 @@
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Svarttjärnen 6, Vrm</t>
+          <t>Svarttjärnen 11, Vrm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>404984</v>
+        <v>404831</v>
       </c>
       <c r="R74" t="n">
-        <v>6687077</v>
+        <v>6686875</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8831,7 +8831,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>123483866</v>
+        <v>123484005</v>
       </c>
       <c r="B75" t="n">
         <v>78788</v>
@@ -8870,14 +8870,14 @@
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Svarttjärnen 6, Vrm</t>
+          <t>Svarttjärnen 10, Vrm</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>404984</v>
+        <v>404746</v>
       </c>
       <c r="R75" t="n">
-        <v>6687077</v>
+        <v>6686832</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8937,10 +8937,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>123484000</v>
+        <v>123483987</v>
       </c>
       <c r="B76" t="n">
-        <v>78524</v>
+        <v>78788</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8953,21 +8953,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8976,14 +8976,14 @@
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Svarttjärnen 9, Vrm</t>
+          <t>Svarttjärnen 8, Vrm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>404763</v>
+        <v>404649</v>
       </c>
       <c r="R76" t="n">
-        <v>6686809</v>
+        <v>6686758</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9043,10 +9043,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>123484009</v>
+        <v>123483891</v>
       </c>
       <c r="B77" t="n">
-        <v>78788</v>
+        <v>78524</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9059,21 +9059,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9082,14 +9082,14 @@
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Svarttjärnen 11, Vrm</t>
+          <t>Svarttjärnen 7, Vrm</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>404831</v>
+        <v>404939</v>
       </c>
       <c r="R77" t="n">
-        <v>6686875</v>
+        <v>6687011</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9149,7 +9149,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>123483891</v>
+        <v>123484000</v>
       </c>
       <c r="B78" t="n">
         <v>78524</v>
@@ -9188,14 +9188,14 @@
       <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Svarttjärnen 7, Vrm</t>
+          <t>Svarttjärnen 9, Vrm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>404939</v>
+        <v>404763</v>
       </c>
       <c r="R78" t="n">
-        <v>6687011</v>
+        <v>6686809</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9255,10 +9255,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>123483987</v>
+        <v>123484017</v>
       </c>
       <c r="B79" t="n">
-        <v>78788</v>
+        <v>78525</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9271,21 +9271,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9294,14 +9294,14 @@
       <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Svarttjärnen 8, Vrm</t>
+          <t>Svarttjärnen 12, Vrm</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>404649</v>
+        <v>404849</v>
       </c>
       <c r="R79" t="n">
-        <v>6686758</v>
+        <v>6686889</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>

--- a/artfynd/A 6315-2025 artfynd.xlsx
+++ b/artfynd/A 6315-2025 artfynd.xlsx
@@ -5555,10 +5555,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123302244</v>
+        <v>123302239</v>
       </c>
       <c r="B43" t="n">
-        <v>78788</v>
+        <v>96332</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5571,21 +5571,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>404831</v>
+        <v>404942</v>
       </c>
       <c r="R43" t="n">
-        <v>6686961</v>
+        <v>6686972</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5657,10 +5657,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123302255</v>
+        <v>123302237</v>
       </c>
       <c r="B44" t="n">
-        <v>78788</v>
+        <v>78524</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5673,21 +5673,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5697,10 +5697,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>404742</v>
+        <v>404784</v>
       </c>
       <c r="R44" t="n">
-        <v>6686791</v>
+        <v>6686893</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5759,10 +5759,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123302234</v>
+        <v>123302254</v>
       </c>
       <c r="B45" t="n">
-        <v>78788</v>
+        <v>96332</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5775,21 +5775,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5799,10 +5799,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>404896</v>
+        <v>404893</v>
       </c>
       <c r="R45" t="n">
-        <v>6686928</v>
+        <v>6687000</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5861,7 +5861,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123302250</v>
+        <v>123302242</v>
       </c>
       <c r="B46" t="n">
         <v>78788</v>
@@ -5901,10 +5901,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>404749</v>
+        <v>404779</v>
       </c>
       <c r="R46" t="n">
-        <v>6686779</v>
+        <v>6686907</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5963,10 +5963,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123302261</v>
+        <v>123302238</v>
       </c>
       <c r="B47" t="n">
-        <v>78525</v>
+        <v>92271</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5975,25 +5975,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -6003,10 +6003,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>404755</v>
+        <v>404664</v>
       </c>
       <c r="R47" t="n">
-        <v>6686809</v>
+        <v>6686821</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6065,7 +6065,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123302249</v>
+        <v>123302240</v>
       </c>
       <c r="B48" t="n">
         <v>96332</v>
@@ -6105,10 +6105,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>404925</v>
+        <v>404906</v>
       </c>
       <c r="R48" t="n">
-        <v>6687022</v>
+        <v>6686997</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6167,10 +6167,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123302251</v>
+        <v>123302262</v>
       </c>
       <c r="B49" t="n">
-        <v>78788</v>
+        <v>78524</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6183,21 +6183,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6207,10 +6207,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>404754</v>
+        <v>404991</v>
       </c>
       <c r="R49" t="n">
-        <v>6686824</v>
+        <v>6687033</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6269,10 +6269,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123302240</v>
+        <v>123302234</v>
       </c>
       <c r="B50" t="n">
-        <v>96332</v>
+        <v>78788</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6285,21 +6285,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6309,10 +6309,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>404906</v>
+        <v>404896</v>
       </c>
       <c r="R50" t="n">
-        <v>6686997</v>
+        <v>6686928</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6371,7 +6371,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123302263</v>
+        <v>123302244</v>
       </c>
       <c r="B51" t="n">
         <v>78788</v>
@@ -6411,10 +6411,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>405174</v>
+        <v>404831</v>
       </c>
       <c r="R51" t="n">
-        <v>6687209</v>
+        <v>6686961</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6473,10 +6473,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123302237</v>
+        <v>123302241</v>
       </c>
       <c r="B52" t="n">
-        <v>78524</v>
+        <v>78788</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6489,21 +6489,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6513,7 +6513,7 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>404784</v>
+        <v>404765</v>
       </c>
       <c r="R52" t="n">
         <v>6686893</v>
@@ -6575,10 +6575,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123302253</v>
+        <v>123302256</v>
       </c>
       <c r="B53" t="n">
-        <v>96332</v>
+        <v>92271</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6587,25 +6587,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>53</v>
+        <v>4364</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6615,10 +6615,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>404899</v>
+        <v>404740</v>
       </c>
       <c r="R53" t="n">
-        <v>6686991</v>
+        <v>6686779</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6677,10 +6677,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123302256</v>
+        <v>123302249</v>
       </c>
       <c r="B54" t="n">
-        <v>92271</v>
+        <v>96332</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6689,25 +6689,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4364</v>
+        <v>53</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6717,10 +6717,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>404740</v>
+        <v>404925</v>
       </c>
       <c r="R54" t="n">
-        <v>6686779</v>
+        <v>6687022</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6779,7 +6779,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123302257</v>
+        <v>123302247</v>
       </c>
       <c r="B55" t="n">
         <v>78788</v>
@@ -6819,10 +6819,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>404825</v>
+        <v>404900</v>
       </c>
       <c r="R55" t="n">
-        <v>6686922</v>
+        <v>6686936</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6881,10 +6881,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123302262</v>
+        <v>123302235</v>
       </c>
       <c r="B56" t="n">
-        <v>78524</v>
+        <v>78788</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6897,21 +6897,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6921,10 +6921,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>404991</v>
+        <v>404825</v>
       </c>
       <c r="R56" t="n">
-        <v>6687033</v>
+        <v>6686897</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6983,10 +6983,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123302243</v>
+        <v>123302250</v>
       </c>
       <c r="B57" t="n">
-        <v>82575</v>
+        <v>78788</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6999,21 +6999,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7023,10 +7023,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>404663</v>
+        <v>404749</v>
       </c>
       <c r="R57" t="n">
-        <v>6686805</v>
+        <v>6686779</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7085,7 +7085,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123302247</v>
+        <v>123302255</v>
       </c>
       <c r="B58" t="n">
         <v>78788</v>
@@ -7125,10 +7125,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>404900</v>
+        <v>404742</v>
       </c>
       <c r="R58" t="n">
-        <v>6686936</v>
+        <v>6686791</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7187,10 +7187,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123302241</v>
+        <v>123302243</v>
       </c>
       <c r="B59" t="n">
-        <v>78788</v>
+        <v>82575</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7203,21 +7203,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7227,10 +7227,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>404765</v>
+        <v>404663</v>
       </c>
       <c r="R59" t="n">
-        <v>6686893</v>
+        <v>6686805</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7289,7 +7289,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123302259</v>
+        <v>123302263</v>
       </c>
       <c r="B60" t="n">
         <v>78788</v>
@@ -7329,10 +7329,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>404680</v>
+        <v>405174</v>
       </c>
       <c r="R60" t="n">
-        <v>6686815</v>
+        <v>6687209</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7391,10 +7391,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123302238</v>
+        <v>123302252</v>
       </c>
       <c r="B61" t="n">
-        <v>92271</v>
+        <v>78788</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7403,25 +7403,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7431,10 +7431,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>404664</v>
+        <v>404884</v>
       </c>
       <c r="R61" t="n">
-        <v>6686821</v>
+        <v>6686940</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7493,7 +7493,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123302246</v>
+        <v>123302258</v>
       </c>
       <c r="B62" t="n">
         <v>78788</v>
@@ -7533,10 +7533,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>404908</v>
+        <v>404812</v>
       </c>
       <c r="R62" t="n">
-        <v>6687022</v>
+        <v>6686926</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7595,10 +7595,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123302239</v>
+        <v>123302259</v>
       </c>
       <c r="B63" t="n">
-        <v>96332</v>
+        <v>78788</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7611,21 +7611,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7635,10 +7635,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>404942</v>
+        <v>404680</v>
       </c>
       <c r="R63" t="n">
-        <v>6686972</v>
+        <v>6686815</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7697,10 +7697,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123302254</v>
+        <v>123302264</v>
       </c>
       <c r="B64" t="n">
-        <v>96332</v>
+        <v>92306</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7713,21 +7713,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>53</v>
+        <v>5966</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7737,10 +7737,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>404893</v>
+        <v>405076</v>
       </c>
       <c r="R64" t="n">
-        <v>6687000</v>
+        <v>6687116</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7799,10 +7799,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>123302242</v>
+        <v>123302261</v>
       </c>
       <c r="B65" t="n">
-        <v>78788</v>
+        <v>78525</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7815,21 +7815,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7839,10 +7839,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>404779</v>
+        <v>404755</v>
       </c>
       <c r="R65" t="n">
-        <v>6686907</v>
+        <v>6686809</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7901,7 +7901,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>123302248</v>
+        <v>123302246</v>
       </c>
       <c r="B66" t="n">
         <v>78788</v>
@@ -7941,10 +7941,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>404485</v>
+        <v>404908</v>
       </c>
       <c r="R66" t="n">
-        <v>6686609</v>
+        <v>6687022</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8003,7 +8003,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>123302258</v>
+        <v>123302257</v>
       </c>
       <c r="B67" t="n">
         <v>78788</v>
@@ -8043,10 +8043,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>404812</v>
+        <v>404825</v>
       </c>
       <c r="R67" t="n">
-        <v>6686926</v>
+        <v>6686922</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8105,7 +8105,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>123302252</v>
+        <v>123302251</v>
       </c>
       <c r="B68" t="n">
         <v>78788</v>
@@ -8145,10 +8145,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>404884</v>
+        <v>404754</v>
       </c>
       <c r="R68" t="n">
-        <v>6686940</v>
+        <v>6686824</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8207,10 +8207,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>123302236</v>
+        <v>123302253</v>
       </c>
       <c r="B69" t="n">
-        <v>78525</v>
+        <v>96332</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8223,21 +8223,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>228912</v>
+        <v>53</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8247,10 +8247,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>404784</v>
+        <v>404899</v>
       </c>
       <c r="R69" t="n">
-        <v>6686893</v>
+        <v>6686991</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8309,7 +8309,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>123302235</v>
+        <v>123302248</v>
       </c>
       <c r="B70" t="n">
         <v>78788</v>
@@ -8349,10 +8349,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>404825</v>
+        <v>404485</v>
       </c>
       <c r="R70" t="n">
-        <v>6686897</v>
+        <v>6686609</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8411,10 +8411,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>123302264</v>
+        <v>123302236</v>
       </c>
       <c r="B71" t="n">
-        <v>92306</v>
+        <v>78525</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8427,21 +8427,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5966</v>
+        <v>228912</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8451,10 +8451,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>405076</v>
+        <v>404784</v>
       </c>
       <c r="R71" t="n">
-        <v>6687116</v>
+        <v>6686893</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8513,7 +8513,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>123483866</v>
+        <v>123483987</v>
       </c>
       <c r="B72" t="n">
         <v>78788</v>
@@ -8552,14 +8552,14 @@
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Svarttjärnen 6, Vrm</t>
+          <t>Svarttjärnen 8, Vrm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>404984</v>
+        <v>404649</v>
       </c>
       <c r="R72" t="n">
-        <v>6687077</v>
+        <v>6686758</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8619,7 +8619,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>123483876</v>
+        <v>123484017</v>
       </c>
       <c r="B73" t="n">
         <v>78525</v>
@@ -8658,14 +8658,14 @@
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Svarttjärnen 6, Vrm</t>
+          <t>Svarttjärnen 12, Vrm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>404984</v>
+        <v>404849</v>
       </c>
       <c r="R73" t="n">
-        <v>6687077</v>
+        <v>6686889</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8725,10 +8725,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>123484009</v>
+        <v>123484000</v>
       </c>
       <c r="B74" t="n">
-        <v>78788</v>
+        <v>78524</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8741,21 +8741,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8764,14 +8764,14 @@
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Svarttjärnen 11, Vrm</t>
+          <t>Svarttjärnen 9, Vrm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>404831</v>
+        <v>404763</v>
       </c>
       <c r="R74" t="n">
-        <v>6686875</v>
+        <v>6686809</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8937,10 +8937,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>123483987</v>
+        <v>123483876</v>
       </c>
       <c r="B76" t="n">
-        <v>78788</v>
+        <v>78525</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8953,21 +8953,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8976,14 +8976,14 @@
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Svarttjärnen 8, Vrm</t>
+          <t>Svarttjärnen 6, Vrm</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>404649</v>
+        <v>404984</v>
       </c>
       <c r="R76" t="n">
-        <v>6686758</v>
+        <v>6687077</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9149,10 +9149,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>123484000</v>
+        <v>123484009</v>
       </c>
       <c r="B78" t="n">
-        <v>78524</v>
+        <v>78788</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9165,21 +9165,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9188,14 +9188,14 @@
       <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Svarttjärnen 9, Vrm</t>
+          <t>Svarttjärnen 11, Vrm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>404763</v>
+        <v>404831</v>
       </c>
       <c r="R78" t="n">
-        <v>6686809</v>
+        <v>6686875</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9255,10 +9255,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>123484017</v>
+        <v>123483866</v>
       </c>
       <c r="B79" t="n">
-        <v>78525</v>
+        <v>78788</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9271,21 +9271,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9294,14 +9294,14 @@
       <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Svarttjärnen 12, Vrm</t>
+          <t>Svarttjärnen 6, Vrm</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>404849</v>
+        <v>404984</v>
       </c>
       <c r="R79" t="n">
-        <v>6686889</v>
+        <v>6687077</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>

--- a/artfynd/A 6315-2025 artfynd.xlsx
+++ b/artfynd/A 6315-2025 artfynd.xlsx
@@ -5759,10 +5759,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123302254</v>
+        <v>123302242</v>
       </c>
       <c r="B45" t="n">
-        <v>96332</v>
+        <v>78788</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5775,21 +5775,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5799,10 +5799,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>404893</v>
+        <v>404779</v>
       </c>
       <c r="R45" t="n">
-        <v>6687000</v>
+        <v>6686907</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5861,10 +5861,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123302242</v>
+        <v>123302254</v>
       </c>
       <c r="B46" t="n">
-        <v>78788</v>
+        <v>96332</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5877,21 +5877,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5901,10 +5901,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>404779</v>
+        <v>404893</v>
       </c>
       <c r="R46" t="n">
-        <v>6686907</v>
+        <v>6687000</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -7697,10 +7697,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123302264</v>
+        <v>123302261</v>
       </c>
       <c r="B64" t="n">
-        <v>92306</v>
+        <v>78525</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7713,21 +7713,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5966</v>
+        <v>228912</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7737,10 +7737,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>405076</v>
+        <v>404755</v>
       </c>
       <c r="R64" t="n">
-        <v>6687116</v>
+        <v>6686809</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7799,10 +7799,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>123302261</v>
+        <v>123302264</v>
       </c>
       <c r="B65" t="n">
-        <v>78525</v>
+        <v>92306</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7815,21 +7815,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>228912</v>
+        <v>5966</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7839,10 +7839,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>404755</v>
+        <v>405076</v>
       </c>
       <c r="R65" t="n">
-        <v>6686809</v>
+        <v>6687116</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>

--- a/artfynd/A 6315-2025 artfynd.xlsx
+++ b/artfynd/A 6315-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY135"/>
+  <dimension ref="A1:AZ135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67516440</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67516442</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -977,6 +992,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123025220</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1074,6 +1094,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123302239</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1171,6 +1196,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123302240</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1268,6 +1298,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123302249</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1365,6 +1400,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123302253</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1462,6 +1502,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123302254</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1559,6 +1604,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123302260</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1666,6 +1716,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74689995</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1773,6 +1828,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74690015</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1874,6 +1934,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104582275</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1981,6 +2046,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74689892</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2088,6 +2158,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74689912</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2195,6 +2270,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74689994</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2302,6 +2382,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74690012</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2409,6 +2494,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74690013</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2516,6 +2606,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74689973</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2623,6 +2718,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74689890</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2730,6 +2830,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74689964</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2837,6 +2942,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74689996</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2944,6 +3054,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74690017</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3051,6 +3166,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74690018</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3148,6 +3268,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123302243</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3255,6 +3380,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74689987</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3362,6 +3492,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74689989</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3468,6 +3603,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123025199</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3570,6 +3710,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74689992</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3667,6 +3812,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123302238</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3764,6 +3914,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123302256</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3861,6 +4016,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123302264</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3958,6 +4118,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67516441</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4065,6 +4230,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74689872</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4172,6 +4342,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74689876</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4279,6 +4454,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74689877</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4386,6 +4566,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74689878</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4493,6 +4678,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74689879</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4600,6 +4790,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74689886</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4707,6 +4902,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74689901</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4814,6 +5014,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74689902</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4921,6 +5126,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74689903</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5028,6 +5238,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74689915</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5135,6 +5350,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74689924</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5242,6 +5462,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74689925</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5349,6 +5574,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74689929</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5456,6 +5686,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74689930</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5563,6 +5798,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74689967</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5670,6 +5910,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74689970</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5777,6 +6022,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74689971</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5884,6 +6134,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74689972</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5991,6 +6246,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74689975</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6098,6 +6358,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74689991</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6205,6 +6470,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74689993</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6312,6 +6582,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74689997</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6419,6 +6694,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74689998</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6526,6 +6806,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74690001</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6633,6 +6918,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74690011</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6740,6 +7030,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74690014</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6847,6 +7142,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74690016</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6954,6 +7254,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74690020</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7059,6 +7364,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123024336</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7164,6 +7474,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123024872</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7269,6 +7584,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123025268</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7366,6 +7686,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123302234</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7463,6 +7788,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123302235</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7560,6 +7890,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123302241</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7657,6 +7992,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123302242</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7754,6 +8094,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123302244</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7851,6 +8196,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123302246</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7948,6 +8298,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123302247</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8045,6 +8400,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123302248</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8142,6 +8502,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123302250</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8239,6 +8604,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123302251</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8336,6 +8706,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123302252</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8433,6 +8808,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123302255</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8530,6 +8910,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123302257</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8627,6 +9012,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123302258</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8724,6 +9114,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123302259</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8821,6 +9216,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123302263</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8922,6 +9322,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123483866</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9023,6 +9428,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123483987</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9124,6 +9534,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123484005</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9225,6 +9640,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123484009</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9326,6 +9746,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104582277</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9433,6 +9858,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74689889</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9540,6 +9970,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74689895</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9647,6 +10082,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74689897</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9754,6 +10194,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74689909</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9861,6 +10306,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74689911</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9968,6 +10418,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74689917</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10075,6 +10530,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74689919</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10182,6 +10642,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74689921</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10289,6 +10754,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74689928</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10396,6 +10866,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74689963</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10503,6 +10978,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74689966</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10610,6 +11090,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74689969</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10717,6 +11202,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74689990</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10814,6 +11304,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123302237</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10911,6 +11406,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123302262</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11012,6 +11512,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123483891</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11113,6 +11618,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123484000</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11220,6 +11730,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74690019</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11317,6 +11832,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67516439</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11424,6 +11944,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74689881</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11531,6 +12056,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74689893</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11638,6 +12168,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74689898</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11745,6 +12280,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74689907</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11852,6 +12392,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74689913</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -11959,6 +12504,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74689922</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -12066,6 +12616,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74689926</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -12173,6 +12728,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74689988</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -12280,6 +12840,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74689999</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -12387,6 +12952,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74690010</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12484,6 +13054,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123302245</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -12591,6 +13166,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74689888</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -12698,6 +13278,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74689891</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -12805,6 +13390,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74689894</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -12912,6 +13502,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74689896</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -13019,6 +13614,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74689899</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -13126,6 +13726,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74689908</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -13233,6 +13838,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74689910</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -13340,6 +13950,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74689914</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -13447,6 +14062,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74689916</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -13554,6 +14174,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74689918</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -13661,6 +14286,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74689920</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -13768,6 +14398,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74689927</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -13875,6 +14510,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74689962</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -13982,6 +14622,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74689965</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -14089,6 +14734,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74689968</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -14194,6 +14844,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123025288</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -14291,6 +14946,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123302236</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -14388,6 +15048,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123302261</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -14489,6 +15154,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123483876</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -14590,8 +15260,149 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123484017</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>